--- a/OMOP Analysis/Results/Output_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP.xlsx
@@ -400,25 +400,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>64.39</v>
+        <v>13.47</v>
       </c>
       <c r="B2">
         <v>0.49</v>
       </c>
       <c r="C2">
-        <v>131851.5</v>
+        <v>1441</v>
       </c>
       <c r="D2">
-        <v>3217.39</v>
+        <v>32.75</v>
       </c>
       <c r="E2">
-        <v>54.28</v>
+        <v>11.44</v>
       </c>
       <c r="F2">
-        <v>29.12</v>
+        <v>5.92</v>
       </c>
       <c r="G2">
-        <v>115.59</v>
+        <v>21.71</v>
       </c>
     </row>
   </sheetData>
@@ -470,25 +470,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>64.22</v>
+        <v>13.07</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>131851.5</v>
+        <v>1441</v>
       </c>
       <c r="D2">
-        <v>3213.25</v>
+        <v>32.25</v>
       </c>
       <c r="E2">
-        <v>53.79</v>
+        <v>10.86</v>
       </c>
       <c r="F2">
-        <v>29.12</v>
+        <v>4.93</v>
       </c>
       <c r="G2">
-        <v>115.46</v>
+        <v>21.22</v>
       </c>
     </row>
   </sheetData>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -545,22 +545,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>1419</v>
+        <v>289</v>
       </c>
       <c r="C2">
-        <v>4.3</v>
+        <v>1.88</v>
       </c>
       <c r="D2">
-        <v>77.05</v>
+        <v>2.77</v>
       </c>
       <c r="E2">
         <v>0.49</v>
       </c>
       <c r="F2">
-        <v>1080.75</v>
+        <v>16.56</v>
       </c>
       <c r="G2">
-        <v>206</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="C3">
-        <v>10.32</v>
+        <v>3.83</v>
       </c>
       <c r="D3">
-        <v>2702.38</v>
+        <v>7.44</v>
       </c>
       <c r="E3">
         <v>0.49</v>
       </c>
       <c r="F3">
-        <v>12608.75</v>
+        <v>25.73</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -595,22 +595,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="D4">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="E4">
-        <v>0.49</v>
+        <v>0.99</v>
       </c>
       <c r="F4">
-        <v>3.39</v>
+        <v>2.47</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -620,22 +620,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>2.41</v>
+        <v>1.32</v>
       </c>
       <c r="D5">
-        <v>2.35</v>
+        <v>0.74</v>
       </c>
       <c r="E5">
         <v>0.49</v>
       </c>
       <c r="F5">
-        <v>6.91</v>
+        <v>2.47</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>746</v>
+        <v>270</v>
       </c>
       <c r="C6">
-        <v>2.07</v>
+        <v>1.2</v>
       </c>
       <c r="D6">
-        <v>519.5700000000001</v>
+        <v>2.14</v>
       </c>
       <c r="E6">
         <v>0.49</v>
       </c>
       <c r="F6">
-        <v>7565.25</v>
+        <v>15.14</v>
       </c>
       <c r="G6">
-        <v>212</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>10366</v>
+        <v>2073</v>
       </c>
       <c r="C7">
-        <v>5.56</v>
+        <v>2.79</v>
       </c>
       <c r="D7">
-        <v>285.3</v>
+        <v>5.3</v>
       </c>
       <c r="E7">
         <v>0.49</v>
       </c>
       <c r="F7">
-        <v>9726.75</v>
+        <v>37.27</v>
       </c>
       <c r="G7">
-        <v>1221</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>9909</v>
+        <v>1894</v>
       </c>
       <c r="C8">
-        <v>5.08</v>
+        <v>1.78</v>
       </c>
       <c r="D8">
-        <v>132.41</v>
+        <v>3.65</v>
       </c>
       <c r="E8">
         <v>0.49</v>
       </c>
       <c r="F8">
-        <v>2665.85</v>
+        <v>39.24</v>
       </c>
       <c r="G8">
-        <v>1224</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9">
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>769</v>
+        <v>189</v>
       </c>
       <c r="C9">
-        <v>3.09</v>
+        <v>1.71</v>
       </c>
       <c r="D9">
-        <v>36.02</v>
+        <v>4.74</v>
       </c>
       <c r="E9">
         <v>0.49</v>
       </c>
       <c r="F9">
-        <v>360.25</v>
+        <v>34.13</v>
       </c>
       <c r="G9">
-        <v>154</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -767,22 +767,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>1.23</v>
-      </c>
-      <c r="D11">
-        <v>1.55</v>
+        <v>4.24</v>
       </c>
       <c r="E11">
-        <v>0.49</v>
+        <v>4.24</v>
       </c>
       <c r="F11">
         <v>4.24</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -792,22 +789,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>3.13</v>
+        <v>1.17</v>
       </c>
       <c r="D12">
-        <v>323.22</v>
+        <v>3.18</v>
       </c>
       <c r="E12">
         <v>0.49</v>
       </c>
       <c r="F12">
-        <v>1801.25</v>
+        <v>13.1</v>
       </c>
       <c r="G12">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -817,22 +814,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>848</v>
+        <v>113</v>
       </c>
       <c r="C13">
-        <v>2.79</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>123.92</v>
+        <v>1.07</v>
       </c>
       <c r="E13">
         <v>0.49</v>
       </c>
       <c r="F13">
-        <v>1501.04</v>
+        <v>5.43</v>
       </c>
       <c r="G13">
-        <v>194</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -842,22 +839,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="D14">
-        <v>2.89</v>
+        <v>1.02</v>
       </c>
       <c r="E14">
         <v>0.49</v>
       </c>
       <c r="F14">
-        <v>7.75</v>
+        <v>1.94</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -867,22 +864,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>1.73</v>
+        <v>0.74</v>
       </c>
       <c r="D15">
-        <v>1.09</v>
+        <v>0.28</v>
       </c>
       <c r="E15">
         <v>0.49</v>
       </c>
       <c r="F15">
-        <v>2.96</v>
+        <v>0.99</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -892,22 +889,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="D16">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="E16">
         <v>0.49</v>
       </c>
       <c r="F16">
-        <v>11.38</v>
+        <v>4.74</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -917,22 +914,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>357</v>
+        <v>77</v>
       </c>
       <c r="C17">
-        <v>3.94</v>
+        <v>1.16</v>
       </c>
       <c r="D17">
-        <v>7.83</v>
+        <v>2.14</v>
       </c>
       <c r="E17">
         <v>0.49</v>
       </c>
       <c r="F17">
-        <v>48.97</v>
+        <v>13.34</v>
       </c>
       <c r="G17">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -942,22 +939,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="D18">
-        <v>12.82</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0.49</v>
       </c>
       <c r="F18">
-        <v>32.75</v>
+        <v>0.49</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -967,22 +964,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>1.86</v>
+        <v>0.99</v>
       </c>
       <c r="D19">
-        <v>4.38</v>
+        <v>0.85</v>
       </c>
       <c r="E19">
         <v>0.49</v>
       </c>
       <c r="F19">
-        <v>17.32</v>
+        <v>1.97</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -992,22 +989,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>467</v>
+        <v>98</v>
       </c>
       <c r="C20">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="D20">
-        <v>63.96</v>
+        <v>1.62</v>
       </c>
       <c r="E20">
         <v>0.49</v>
       </c>
       <c r="F20">
-        <v>720.5</v>
+        <v>7.9</v>
       </c>
       <c r="G20">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -1017,22 +1014,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>72699</v>
+        <v>15043</v>
       </c>
       <c r="C21">
-        <v>6.44</v>
+        <v>2.3</v>
       </c>
       <c r="D21">
-        <v>390.08</v>
+        <v>6.08</v>
       </c>
       <c r="E21">
         <v>0.49</v>
       </c>
       <c r="F21">
-        <v>11528</v>
+        <v>159.83</v>
       </c>
       <c r="G21">
-        <v>7261</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="22">
@@ -1042,22 +1039,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>248016</v>
+        <v>42305</v>
       </c>
       <c r="C22">
-        <v>9.08</v>
+        <v>2.59</v>
       </c>
       <c r="D22">
-        <v>458.13</v>
+        <v>6.24</v>
       </c>
       <c r="E22">
         <v>0.49</v>
       </c>
       <c r="F22">
-        <v>21975.25</v>
+        <v>183.9</v>
       </c>
       <c r="G22">
-        <v>17403</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="23">
@@ -1067,22 +1064,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>18180</v>
+        <v>2155</v>
       </c>
       <c r="C23">
-        <v>4.57</v>
+        <v>2.72</v>
       </c>
       <c r="D23">
-        <v>252.58</v>
+        <v>7.74</v>
       </c>
       <c r="E23">
         <v>0.49</v>
       </c>
       <c r="F23">
-        <v>8285.75</v>
+        <v>90.06</v>
       </c>
       <c r="G23">
-        <v>2580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24">
@@ -1092,22 +1089,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>953</v>
+        <v>143</v>
       </c>
       <c r="C24">
-        <v>3.18</v>
+        <v>2.43</v>
       </c>
       <c r="D24">
-        <v>8.1</v>
+        <v>2.94</v>
       </c>
       <c r="E24">
         <v>0.49</v>
       </c>
       <c r="F24">
-        <v>60.04</v>
+        <v>14.8</v>
       </c>
       <c r="G24">
-        <v>178</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -1117,22 +1114,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>524</v>
+        <v>186</v>
       </c>
       <c r="C25">
-        <v>5.94</v>
+        <v>2.94</v>
       </c>
       <c r="D25">
-        <v>561.54</v>
+        <v>20.92</v>
       </c>
       <c r="E25">
         <v>0.49</v>
       </c>
       <c r="F25">
-        <v>4202.92</v>
+        <v>120.08</v>
       </c>
       <c r="G25">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -1142,1163 +1139,1029 @@
         </is>
       </c>
       <c r="B26">
-        <v>536</v>
+        <v>80</v>
       </c>
       <c r="C26">
-        <v>1.22</v>
+        <v>0.82</v>
       </c>
       <c r="D26">
-        <v>27.69</v>
+        <v>1.28</v>
       </c>
       <c r="E26">
         <v>0.49</v>
       </c>
       <c r="F26">
-        <v>360.25</v>
+        <v>7.58</v>
       </c>
       <c r="G26">
-        <v>284</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dietitian Consultant</t>
+          <t>Dietitian Specialist Practitioner</t>
         </is>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0.66</v>
-      </c>
-      <c r="D27">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="E27">
         <v>0.49</v>
       </c>
       <c r="F27">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dietitian Specialist Practitioner</t>
+          <t>Enrolled Nurse</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1618</v>
       </c>
       <c r="C28">
-        <v>0.58</v>
+        <v>1.98</v>
       </c>
       <c r="D28">
-        <v>0.15</v>
+        <v>2.61</v>
       </c>
       <c r="E28">
         <v>0.49</v>
       </c>
       <c r="F28">
-        <v>0.7</v>
+        <v>18.75</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enrolled Nurse</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B29">
-        <v>8363</v>
+        <v>11980</v>
       </c>
       <c r="C29">
-        <v>6.34</v>
+        <v>1.64</v>
       </c>
       <c r="D29">
-        <v>897.7</v>
+        <v>5.28</v>
       </c>
       <c r="E29">
         <v>0.49</v>
       </c>
       <c r="F29">
-        <v>20053.92</v>
+        <v>144.1</v>
       </c>
       <c r="G29">
-        <v>817</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B30">
-        <v>54097</v>
+        <v>296044</v>
       </c>
       <c r="C30">
-        <v>3.45</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="D30">
-        <v>145.18</v>
+        <v>22.16</v>
       </c>
       <c r="E30">
         <v>0.49</v>
       </c>
       <c r="F30">
-        <v>7925.5</v>
+        <v>720.5</v>
       </c>
       <c r="G30">
-        <v>10055</v>
+        <v>21361</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B31">
-        <v>1398908</v>
+        <v>36193</v>
       </c>
       <c r="C31">
-        <v>38.41</v>
+        <v>4.44</v>
       </c>
       <c r="D31">
-        <v>2082.55</v>
+        <v>28.89</v>
       </c>
       <c r="E31">
         <v>0.49</v>
       </c>
       <c r="F31">
-        <v>91863.75</v>
+        <v>720.5</v>
       </c>
       <c r="G31">
-        <v>23226</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Hospital Practitioner</t>
         </is>
       </c>
       <c r="B32">
-        <v>213045</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>10.31</v>
+        <v>1.23</v>
       </c>
       <c r="D32">
-        <v>687.84</v>
+        <v>0.85</v>
       </c>
       <c r="E32">
         <v>0.49</v>
       </c>
       <c r="F32">
-        <v>34944.25</v>
+        <v>1.97</v>
       </c>
       <c r="G32">
-        <v>13329</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hospital Practitioner</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B33">
-        <v>97</v>
+        <v>4561</v>
       </c>
       <c r="C33">
-        <v>3.88</v>
+        <v>2.03</v>
       </c>
       <c r="D33">
-        <v>11.01</v>
+        <v>10.99</v>
       </c>
       <c r="E33">
         <v>0.49</v>
       </c>
       <c r="F33">
-        <v>39.24</v>
+        <v>240.17</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Medical Technical Officer</t>
         </is>
       </c>
       <c r="B34">
-        <v>20815</v>
+        <v>58</v>
       </c>
       <c r="C34">
-        <v>4.83</v>
+        <v>1.04</v>
       </c>
       <c r="D34">
-        <v>222.04</v>
+        <v>1.74</v>
       </c>
       <c r="E34">
         <v>0.49</v>
       </c>
       <c r="F34">
-        <v>4683.25</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G34">
-        <v>2665</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Medical Director</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>767</v>
       </c>
       <c r="C35">
-        <v>1.86</v>
+        <v>1.74</v>
+      </c>
+      <c r="D35">
+        <v>11.72</v>
       </c>
       <c r="E35">
-        <v>1.86</v>
+        <v>0.49</v>
       </c>
       <c r="F35">
-        <v>1.86</v>
+        <v>180.12</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Medical Technical Officer</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B36">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>1.71</v>
+        <v>0.49</v>
       </c>
       <c r="D36">
-        <v>146.76</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0.49</v>
       </c>
       <c r="F36">
-        <v>1080.75</v>
+        <v>0.49</v>
       </c>
       <c r="G36">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B37">
-        <v>3739</v>
+        <v>142</v>
       </c>
       <c r="C37">
-        <v>3.89</v>
+        <v>2.96</v>
       </c>
       <c r="D37">
-        <v>301.28</v>
+        <v>6.79</v>
       </c>
       <c r="E37">
         <v>0.49</v>
       </c>
       <c r="F37">
-        <v>7295.06</v>
+        <v>31.79</v>
       </c>
       <c r="G37">
-        <v>600</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Multi Therapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B38">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>0.72</v>
-      </c>
-      <c r="D38">
-        <v>1.34</v>
+        <v>0.49</v>
       </c>
       <c r="E38">
         <v>0.49</v>
       </c>
       <c r="F38">
-        <v>5.15</v>
+        <v>0.49</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B39">
-        <v>489</v>
+        <v>1401</v>
       </c>
       <c r="C39">
-        <v>4.49</v>
+        <v>1.71</v>
       </c>
       <c r="D39">
-        <v>20.27</v>
+        <v>4.82</v>
       </c>
       <c r="E39">
         <v>0.49</v>
       </c>
       <c r="F39">
-        <v>156.88</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G39">
-        <v>82</v>
+        <v>449</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Multi Therapist</t>
+          <t>Occupational Therapist</t>
         </is>
       </c>
       <c r="B40">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>3.7</v>
+        <v>0.87</v>
       </c>
       <c r="D40">
-        <v>2.22</v>
+        <v>0.66</v>
       </c>
       <c r="E40">
-        <v>1.48</v>
+        <v>0.49</v>
       </c>
       <c r="F40">
-        <v>5.92</v>
+        <v>1.42</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Multi Therapist Specialist Practitioner</t>
+          <t>Optometrist</t>
         </is>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>0.49</v>
+        <v>0.54</v>
+      </c>
+      <c r="D41">
+        <v>0.1</v>
       </c>
       <c r="E41">
         <v>0.49</v>
       </c>
       <c r="F41">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B42">
-        <v>7078</v>
+        <v>95</v>
       </c>
       <c r="C42">
-        <v>5.05</v>
+        <v>6.61</v>
       </c>
       <c r="D42">
-        <v>230.1</v>
+        <v>20</v>
       </c>
       <c r="E42">
-        <v>0.49</v>
+        <v>1.48</v>
       </c>
       <c r="F42">
-        <v>4503.12</v>
+        <v>73.69</v>
       </c>
       <c r="G42">
-        <v>869</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nursery Nurse</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>324</v>
       </c>
       <c r="C43">
-        <v>0.64</v>
+        <v>1.59</v>
       </c>
       <c r="D43">
-        <v>0.63</v>
+        <v>2.98</v>
       </c>
       <c r="E43">
         <v>0.49</v>
       </c>
       <c r="F43">
-        <v>2.18</v>
+        <v>18.01</v>
       </c>
       <c r="G43">
-        <v>7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Occupational Therapist</t>
+          <t>Other Community Health Service - Social Care Worker</t>
         </is>
       </c>
       <c r="B44">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>2.03</v>
-      </c>
-      <c r="D44">
-        <v>20.05</v>
+        <v>2.37</v>
       </c>
       <c r="E44">
-        <v>0.99</v>
+        <v>2.37</v>
       </c>
       <c r="F44">
-        <v>51.46</v>
+        <v>2.37</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Optometrist</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B45">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="C45">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="D45">
-        <v>3.8</v>
+        <v>11.34</v>
       </c>
       <c r="E45">
         <v>0.49</v>
       </c>
       <c r="F45">
-        <v>11.75</v>
+        <v>120.08</v>
       </c>
       <c r="G45">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Paramedic Consultant</t>
         </is>
       </c>
       <c r="B46">
-        <v>375</v>
+        <v>10</v>
       </c>
       <c r="C46">
-        <v>14.48</v>
+        <v>1.08</v>
       </c>
       <c r="D46">
-        <v>63.63</v>
+        <v>1.15</v>
       </c>
       <c r="E46">
         <v>0.49</v>
       </c>
       <c r="F46">
-        <v>191.79</v>
+        <v>3.13</v>
       </c>
       <c r="G46">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B47">
-        <v>1139</v>
+        <v>194</v>
       </c>
       <c r="C47">
-        <v>3.17</v>
+        <v>1.08</v>
       </c>
       <c r="D47">
-        <v>75.84</v>
+        <v>2.26</v>
       </c>
       <c r="E47">
         <v>0.49</v>
       </c>
       <c r="F47">
-        <v>1080.75</v>
+        <v>12.77</v>
       </c>
       <c r="G47">
-        <v>224</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Social Care Worker</t>
+          <t>Patient Welfare Officer</t>
         </is>
       </c>
       <c r="B48">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D48">
-        <v>9.35</v>
+        <v>0.49</v>
       </c>
       <c r="E48">
-        <v>3.37</v>
+        <v>0.49</v>
       </c>
       <c r="F48">
-        <v>16.59</v>
+        <v>0.49</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B49">
-        <v>648</v>
+        <v>497</v>
       </c>
       <c r="C49">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="D49">
-        <v>104.22</v>
+        <v>1.4</v>
       </c>
       <c r="E49">
         <v>0.49</v>
       </c>
       <c r="F49">
-        <v>1441</v>
+        <v>7.9</v>
       </c>
       <c r="G49">
-        <v>271</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Paramedic Consultant</t>
+          <t>Physiotherapist Consultant</t>
         </is>
       </c>
       <c r="B50">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C50">
-        <v>1.38</v>
+        <v>0.72</v>
       </c>
       <c r="D50">
-        <v>3.45</v>
+        <v>0.34</v>
       </c>
       <c r="E50">
         <v>0.49</v>
       </c>
       <c r="F50">
-        <v>12.87</v>
+        <v>1.48</v>
       </c>
       <c r="G50">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Physiotherapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B51">
-        <v>622</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="D51">
-        <v>76.48999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E51">
         <v>0.49</v>
       </c>
       <c r="F51">
-        <v>1080.75</v>
+        <v>2.47</v>
       </c>
       <c r="G51">
-        <v>236</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Patient Welfare Officer</t>
+          <t>Practitioner</t>
         </is>
       </c>
       <c r="B52">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="C52">
-        <v>3.63</v>
+        <v>1.63</v>
       </c>
       <c r="D52">
-        <v>16.78</v>
+        <v>2.32</v>
       </c>
       <c r="E52">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="F52">
-        <v>54.04</v>
+        <v>13.86</v>
       </c>
       <c r="G52">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Pre-reg Pharmacist</t>
         </is>
       </c>
       <c r="B53">
-        <v>2366</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>2.29</v>
-      </c>
-      <c r="D53">
-        <v>365.67</v>
+        <v>0.88</v>
       </c>
       <c r="E53">
-        <v>0.49</v>
+        <v>0.88</v>
       </c>
       <c r="F53">
-        <v>9006.25</v>
+        <v>0.88</v>
       </c>
       <c r="G53">
-        <v>629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Physiotherapist Consultant</t>
+          <t>Psychotherapist</t>
         </is>
       </c>
       <c r="B54">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="C54">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="D54">
-        <v>8.41</v>
+        <v>0.99</v>
       </c>
       <c r="E54">
         <v>0.49</v>
       </c>
       <c r="F54">
-        <v>40.94</v>
+        <v>2.47</v>
       </c>
       <c r="G54">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Physiotherapist Specialist Practitioner</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="B55">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="C55">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="D55">
-        <v>10.28</v>
+        <v>1.5</v>
       </c>
       <c r="E55">
         <v>0.49</v>
       </c>
       <c r="F55">
-        <v>65.5</v>
+        <v>5.51</v>
       </c>
       <c r="G55">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Practitioner</t>
+          <t>Regional Dental Officer</t>
         </is>
       </c>
       <c r="B56">
-        <v>1513</v>
+        <v>13</v>
       </c>
       <c r="C56">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="D56">
-        <v>128.78</v>
+        <v>2.02</v>
       </c>
       <c r="E56">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="F56">
-        <v>1756.22</v>
+        <v>4.44</v>
       </c>
       <c r="G56">
-        <v>227</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pre-reg Pharmacist</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>26459</v>
       </c>
       <c r="C57">
-        <v>0.88</v>
+        <v>3.17</v>
+      </c>
+      <c r="D57">
+        <v>11.46</v>
       </c>
       <c r="E57">
-        <v>0.88</v>
+        <v>0.49</v>
       </c>
       <c r="F57">
-        <v>0.88</v>
+        <v>360.25</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>4934</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Psychotherapist</t>
+          <t>Senior House Officer</t>
         </is>
       </c>
       <c r="B58">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C58">
-        <v>3.51</v>
+        <v>1.55</v>
       </c>
       <c r="D58">
-        <v>96.45999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="E58">
         <v>0.49</v>
       </c>
       <c r="F58">
-        <v>360.25</v>
+        <v>9.01</v>
       </c>
       <c r="G58">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Radiologist</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B59">
-        <v>220</v>
+        <v>12099</v>
       </c>
       <c r="C59">
-        <v>5.15</v>
+        <v>2.12</v>
       </c>
       <c r="D59">
-        <v>20.5</v>
+        <v>17.13</v>
       </c>
       <c r="E59">
         <v>0.49</v>
       </c>
       <c r="F59">
-        <v>102.93</v>
+        <v>720.5</v>
       </c>
       <c r="G59">
-        <v>26</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Regional Dental Officer</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B60">
-        <v>39</v>
+        <v>2506</v>
       </c>
       <c r="C60">
-        <v>3.56</v>
+        <v>2.01</v>
       </c>
       <c r="D60">
-        <v>3.97</v>
+        <v>4.44</v>
       </c>
       <c r="E60">
         <v>0.49</v>
       </c>
       <c r="F60">
-        <v>11.34</v>
+        <v>51.82</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>704</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B61">
-        <v>110815</v>
+        <v>7</v>
       </c>
       <c r="C61">
-        <v>8.52</v>
+        <v>3.62</v>
       </c>
       <c r="D61">
-        <v>430.02</v>
+        <v>2.08</v>
       </c>
       <c r="E61">
-        <v>0.49</v>
+        <v>1.62</v>
       </c>
       <c r="F61">
-        <v>15130.5</v>
+        <v>4.56</v>
       </c>
       <c r="G61">
-        <v>8276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior House Officer</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B62">
-        <v>148</v>
+        <v>11822</v>
       </c>
       <c r="C62">
-        <v>2.81</v>
+        <v>1.99</v>
       </c>
       <c r="D62">
-        <v>15.24</v>
+        <v>5.04</v>
       </c>
       <c r="E62">
         <v>0.49</v>
       </c>
       <c r="F62">
-        <v>72.05</v>
+        <v>180.12</v>
       </c>
       <c r="G62">
-        <v>39</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B63">
-        <v>56346</v>
+        <v>138</v>
       </c>
       <c r="C63">
-        <v>5.07</v>
+        <v>1.85</v>
       </c>
       <c r="D63">
-        <v>405.39</v>
+        <v>1.58</v>
       </c>
       <c r="E63">
         <v>0.49</v>
       </c>
       <c r="F63">
-        <v>20894.5</v>
+        <v>7.58</v>
       </c>
       <c r="G63">
-        <v>7107</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Specialist Registrar</t>
         </is>
       </c>
       <c r="B64">
-        <v>12724</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>6.38</v>
-      </c>
-      <c r="D64">
-        <v>663.1</v>
+        <v>1.17</v>
       </c>
       <c r="E64">
-        <v>0.49</v>
+        <v>1.17</v>
       </c>
       <c r="F64">
-        <v>20174</v>
+        <v>1.17</v>
       </c>
       <c r="G64">
-        <v>1274</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Social Care Support Worker</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>6702</v>
       </c>
       <c r="C65">
-        <v>4.77</v>
+        <v>2.11</v>
       </c>
       <c r="D65">
-        <v>252.2</v>
+        <v>5.8</v>
       </c>
       <c r="E65">
-        <v>3.59</v>
+        <v>0.49</v>
       </c>
       <c r="F65">
-        <v>360.25</v>
+        <v>144.1</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B66">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C66">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="D66">
-        <v>5.03</v>
+        <v>5.32</v>
       </c>
       <c r="E66">
-        <v>0.49</v>
+        <v>1.43</v>
       </c>
       <c r="F66">
-        <v>11.36</v>
+        <v>19.21</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Trainee Practitioner</t>
         </is>
       </c>
       <c r="B67">
-        <v>58066</v>
+        <v>47</v>
       </c>
       <c r="C67">
-        <v>5.33</v>
+        <v>1.19</v>
       </c>
       <c r="D67">
-        <v>265.02</v>
+        <v>74.86</v>
       </c>
       <c r="E67">
         <v>0.49</v>
       </c>
       <c r="F67">
-        <v>13869.62</v>
+        <v>360.25</v>
       </c>
       <c r="G67">
-        <v>6928</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>692</v>
-      </c>
-      <c r="C68">
-        <v>5.47</v>
-      </c>
-      <c r="D68">
-        <v>21.32</v>
-      </c>
-      <c r="E68">
-        <v>0.49</v>
-      </c>
-      <c r="F68">
-        <v>168.12</v>
-      </c>
-      <c r="G68">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Specialist Registrar</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>18</v>
-      </c>
-      <c r="C69">
-        <v>1.91</v>
-      </c>
-      <c r="D69">
-        <v>118.52</v>
-      </c>
-      <c r="E69">
-        <v>0.49</v>
-      </c>
-      <c r="F69">
-        <v>360.25</v>
-      </c>
-      <c r="G69">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>34968</v>
-      </c>
-      <c r="C70">
-        <v>6.58</v>
-      </c>
-      <c r="D70">
-        <v>404.37</v>
-      </c>
-      <c r="E70">
-        <v>0.49</v>
-      </c>
-      <c r="F70">
-        <v>20894.5</v>
-      </c>
-      <c r="G70">
-        <v>3377</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>134</v>
-      </c>
-      <c r="C71">
-        <v>5.39</v>
-      </c>
-      <c r="D71">
-        <v>19.07</v>
-      </c>
-      <c r="E71">
-        <v>0.49</v>
-      </c>
-      <c r="F71">
-        <v>64.91</v>
-      </c>
-      <c r="G71">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Trainee Practitioner</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>206</v>
-      </c>
-      <c r="C72">
-        <v>1.76</v>
-      </c>
-      <c r="D72">
-        <v>123.93</v>
-      </c>
-      <c r="E72">
-        <v>0.49</v>
-      </c>
-      <c r="F72">
-        <v>1080.75</v>
-      </c>
-      <c r="G72">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2308,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2355,22 +2218,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>1419</v>
+        <v>289</v>
       </c>
       <c r="C2">
-        <v>4.3</v>
+        <v>1.88</v>
       </c>
       <c r="D2">
-        <v>77.05</v>
+        <v>2.77</v>
       </c>
       <c r="E2">
         <v>0.49</v>
       </c>
       <c r="F2">
-        <v>1080.75</v>
+        <v>16.56</v>
       </c>
       <c r="G2">
-        <v>206</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -2380,22 +2243,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="C3">
-        <v>10.32</v>
+        <v>3.83</v>
       </c>
       <c r="D3">
-        <v>2702.38</v>
+        <v>7.44</v>
       </c>
       <c r="E3">
         <v>0.49</v>
       </c>
       <c r="F3">
-        <v>12608.75</v>
+        <v>25.73</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2405,22 +2268,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="D4">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="E4">
-        <v>0.49</v>
+        <v>0.99</v>
       </c>
       <c r="F4">
-        <v>3.39</v>
+        <v>2.47</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2430,22 +2293,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>2.41</v>
+        <v>1.32</v>
       </c>
       <c r="D5">
-        <v>2.35</v>
+        <v>0.74</v>
       </c>
       <c r="E5">
         <v>0.49</v>
       </c>
       <c r="F5">
-        <v>6.91</v>
+        <v>2.47</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2455,22 +2318,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>746</v>
+        <v>270</v>
       </c>
       <c r="C6">
-        <v>2.07</v>
+        <v>1.2</v>
       </c>
       <c r="D6">
-        <v>519.5700000000001</v>
+        <v>2.14</v>
       </c>
       <c r="E6">
         <v>0.49</v>
       </c>
       <c r="F6">
-        <v>7565.25</v>
+        <v>15.14</v>
       </c>
       <c r="G6">
-        <v>212</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -2480,22 +2343,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>10366</v>
+        <v>2073</v>
       </c>
       <c r="C7">
-        <v>5.56</v>
+        <v>2.79</v>
       </c>
       <c r="D7">
-        <v>285.3</v>
+        <v>5.3</v>
       </c>
       <c r="E7">
         <v>0.49</v>
       </c>
       <c r="F7">
-        <v>9726.75</v>
+        <v>37.27</v>
       </c>
       <c r="G7">
-        <v>1221</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -2505,22 +2368,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>9909</v>
+        <v>1894</v>
       </c>
       <c r="C8">
-        <v>5.08</v>
+        <v>1.78</v>
       </c>
       <c r="D8">
-        <v>132.41</v>
+        <v>3.65</v>
       </c>
       <c r="E8">
         <v>0.49</v>
       </c>
       <c r="F8">
-        <v>2665.85</v>
+        <v>39.24</v>
       </c>
       <c r="G8">
-        <v>1224</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9">
@@ -2530,22 +2393,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>769</v>
+        <v>189</v>
       </c>
       <c r="C9">
-        <v>3.09</v>
+        <v>1.71</v>
       </c>
       <c r="D9">
-        <v>36.02</v>
+        <v>4.74</v>
       </c>
       <c r="E9">
         <v>0.49</v>
       </c>
       <c r="F9">
-        <v>360.25</v>
+        <v>34.13</v>
       </c>
       <c r="G9">
-        <v>154</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -2577,22 +2440,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>1.23</v>
-      </c>
-      <c r="D11">
-        <v>1.55</v>
+        <v>4.24</v>
       </c>
       <c r="E11">
-        <v>0.49</v>
+        <v>4.24</v>
       </c>
       <c r="F11">
         <v>4.24</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2602,22 +2462,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>3.13</v>
+        <v>1.17</v>
       </c>
       <c r="D12">
-        <v>323.22</v>
+        <v>3.18</v>
       </c>
       <c r="E12">
         <v>0.49</v>
       </c>
       <c r="F12">
-        <v>1801.25</v>
+        <v>13.1</v>
       </c>
       <c r="G12">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -2627,22 +2487,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>848</v>
+        <v>113</v>
       </c>
       <c r="C13">
-        <v>2.79</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>123.92</v>
+        <v>1.07</v>
       </c>
       <c r="E13">
         <v>0.49</v>
       </c>
       <c r="F13">
-        <v>1501.04</v>
+        <v>5.43</v>
       </c>
       <c r="G13">
-        <v>194</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2652,22 +2512,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="D14">
-        <v>2.89</v>
+        <v>1.02</v>
       </c>
       <c r="E14">
         <v>0.49</v>
       </c>
       <c r="F14">
-        <v>7.75</v>
+        <v>1.94</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2677,22 +2537,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>1.73</v>
+        <v>0.74</v>
       </c>
       <c r="D15">
-        <v>1.09</v>
+        <v>0.28</v>
       </c>
       <c r="E15">
         <v>0.49</v>
       </c>
       <c r="F15">
-        <v>2.96</v>
+        <v>0.99</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2702,22 +2562,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="D16">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="E16">
         <v>0.49</v>
       </c>
       <c r="F16">
-        <v>11.38</v>
+        <v>4.74</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -2727,22 +2587,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>357</v>
+        <v>77</v>
       </c>
       <c r="C17">
-        <v>3.94</v>
+        <v>1.16</v>
       </c>
       <c r="D17">
-        <v>7.83</v>
+        <v>2.14</v>
       </c>
       <c r="E17">
         <v>0.49</v>
       </c>
       <c r="F17">
-        <v>48.97</v>
+        <v>13.34</v>
       </c>
       <c r="G17">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2752,22 +2612,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="D18">
-        <v>12.82</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0.49</v>
       </c>
       <c r="F18">
-        <v>32.75</v>
+        <v>0.49</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2777,22 +2637,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>1.86</v>
+        <v>0.99</v>
       </c>
       <c r="D19">
-        <v>4.38</v>
+        <v>0.85</v>
       </c>
       <c r="E19">
         <v>0.49</v>
       </c>
       <c r="F19">
-        <v>17.32</v>
+        <v>1.97</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2802,22 +2662,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>467</v>
+        <v>98</v>
       </c>
       <c r="C20">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="D20">
-        <v>63.96</v>
+        <v>1.62</v>
       </c>
       <c r="E20">
         <v>0.49</v>
       </c>
       <c r="F20">
-        <v>720.5</v>
+        <v>7.9</v>
       </c>
       <c r="G20">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -2827,22 +2687,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>72699</v>
+        <v>15043</v>
       </c>
       <c r="C21">
-        <v>6.44</v>
+        <v>2.3</v>
       </c>
       <c r="D21">
-        <v>390.08</v>
+        <v>6.08</v>
       </c>
       <c r="E21">
         <v>0.49</v>
       </c>
       <c r="F21">
-        <v>11528</v>
+        <v>159.83</v>
       </c>
       <c r="G21">
-        <v>7261</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="22">
@@ -2852,22 +2712,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>248016</v>
+        <v>42305</v>
       </c>
       <c r="C22">
-        <v>9.08</v>
+        <v>2.59</v>
       </c>
       <c r="D22">
-        <v>458.13</v>
+        <v>6.24</v>
       </c>
       <c r="E22">
         <v>0.49</v>
       </c>
       <c r="F22">
-        <v>21975.25</v>
+        <v>183.9</v>
       </c>
       <c r="G22">
-        <v>17403</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="23">
@@ -2877,22 +2737,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>18180</v>
+        <v>2155</v>
       </c>
       <c r="C23">
-        <v>4.57</v>
+        <v>2.72</v>
       </c>
       <c r="D23">
-        <v>252.58</v>
+        <v>7.74</v>
       </c>
       <c r="E23">
         <v>0.49</v>
       </c>
       <c r="F23">
-        <v>8285.75</v>
+        <v>90.06</v>
       </c>
       <c r="G23">
-        <v>2580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24">
@@ -2902,22 +2762,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>953</v>
+        <v>143</v>
       </c>
       <c r="C24">
-        <v>3.18</v>
+        <v>2.43</v>
       </c>
       <c r="D24">
-        <v>8.1</v>
+        <v>2.94</v>
       </c>
       <c r="E24">
         <v>0.49</v>
       </c>
       <c r="F24">
-        <v>60.04</v>
+        <v>14.8</v>
       </c>
       <c r="G24">
-        <v>178</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -2927,22 +2787,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>524</v>
+        <v>186</v>
       </c>
       <c r="C25">
-        <v>5.94</v>
+        <v>2.94</v>
       </c>
       <c r="D25">
-        <v>561.54</v>
+        <v>20.92</v>
       </c>
       <c r="E25">
         <v>0.49</v>
       </c>
       <c r="F25">
-        <v>4202.92</v>
+        <v>120.08</v>
       </c>
       <c r="G25">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -2952,1188 +2812,1054 @@
         </is>
       </c>
       <c r="B26">
-        <v>536</v>
+        <v>80</v>
       </c>
       <c r="C26">
-        <v>1.22</v>
+        <v>0.82</v>
       </c>
       <c r="D26">
-        <v>27.69</v>
+        <v>1.28</v>
       </c>
       <c r="E26">
         <v>0.49</v>
       </c>
       <c r="F26">
-        <v>360.25</v>
+        <v>7.58</v>
       </c>
       <c r="G26">
-        <v>284</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dietitian Consultant</t>
+          <t>Dietitian Specialist Practitioner</t>
         </is>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0.66</v>
-      </c>
-      <c r="D27">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="E27">
         <v>0.49</v>
       </c>
       <c r="F27">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dietitian Specialist Practitioner</t>
+          <t>Enrolled Nurse</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1618</v>
       </c>
       <c r="C28">
-        <v>0.58</v>
+        <v>1.98</v>
       </c>
       <c r="D28">
-        <v>0.15</v>
+        <v>2.61</v>
       </c>
       <c r="E28">
         <v>0.49</v>
       </c>
       <c r="F28">
-        <v>0.7</v>
+        <v>18.75</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enrolled Nurse</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B29">
-        <v>8363</v>
+        <v>11980</v>
       </c>
       <c r="C29">
-        <v>6.34</v>
+        <v>1.64</v>
       </c>
       <c r="D29">
-        <v>897.7</v>
+        <v>5.28</v>
       </c>
       <c r="E29">
         <v>0.49</v>
       </c>
       <c r="F29">
-        <v>20053.92</v>
+        <v>144.1</v>
       </c>
       <c r="G29">
-        <v>817</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B30">
-        <v>54097</v>
+        <v>296044</v>
       </c>
       <c r="C30">
-        <v>3.45</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="D30">
-        <v>145.18</v>
+        <v>22.16</v>
       </c>
       <c r="E30">
         <v>0.49</v>
       </c>
       <c r="F30">
-        <v>7925.5</v>
+        <v>720.5</v>
       </c>
       <c r="G30">
-        <v>10055</v>
+        <v>21361</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B31">
-        <v>1398908</v>
+        <v>36193</v>
       </c>
       <c r="C31">
-        <v>38.41</v>
+        <v>4.44</v>
       </c>
       <c r="D31">
-        <v>2082.55</v>
+        <v>28.89</v>
       </c>
       <c r="E31">
         <v>0.49</v>
       </c>
       <c r="F31">
-        <v>91863.75</v>
+        <v>720.5</v>
       </c>
       <c r="G31">
-        <v>23226</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Hospital Practitioner</t>
         </is>
       </c>
       <c r="B32">
-        <v>213045</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>10.31</v>
+        <v>1.23</v>
       </c>
       <c r="D32">
-        <v>687.84</v>
+        <v>0.85</v>
       </c>
       <c r="E32">
         <v>0.49</v>
       </c>
       <c r="F32">
-        <v>34944.25</v>
+        <v>1.97</v>
       </c>
       <c r="G32">
-        <v>13329</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hospital Practitioner</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B33">
-        <v>97</v>
+        <v>4561</v>
       </c>
       <c r="C33">
-        <v>3.88</v>
+        <v>2.03</v>
       </c>
       <c r="D33">
-        <v>11.01</v>
+        <v>10.99</v>
       </c>
       <c r="E33">
         <v>0.49</v>
       </c>
       <c r="F33">
-        <v>39.24</v>
+        <v>240.17</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Medical Technical Officer</t>
         </is>
       </c>
       <c r="B34">
-        <v>20815</v>
+        <v>58</v>
       </c>
       <c r="C34">
-        <v>4.83</v>
+        <v>1.04</v>
       </c>
       <c r="D34">
-        <v>222.04</v>
+        <v>1.74</v>
       </c>
       <c r="E34">
         <v>0.49</v>
       </c>
       <c r="F34">
-        <v>4683.25</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G34">
-        <v>2665</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Medical Director</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>767</v>
       </c>
       <c r="C35">
-        <v>1.86</v>
+        <v>1.74</v>
+      </c>
+      <c r="D35">
+        <v>11.72</v>
       </c>
       <c r="E35">
-        <v>1.86</v>
+        <v>0.49</v>
       </c>
       <c r="F35">
-        <v>1.86</v>
+        <v>180.12</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Medical Technical Officer</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B36">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>1.71</v>
+        <v>0.49</v>
       </c>
       <c r="D36">
-        <v>146.76</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0.49</v>
       </c>
       <c r="F36">
-        <v>1080.75</v>
+        <v>0.49</v>
       </c>
       <c r="G36">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B37">
-        <v>3739</v>
+        <v>142</v>
       </c>
       <c r="C37">
-        <v>3.89</v>
+        <v>2.96</v>
       </c>
       <c r="D37">
-        <v>301.28</v>
+        <v>6.79</v>
       </c>
       <c r="E37">
         <v>0.49</v>
       </c>
       <c r="F37">
-        <v>7295.06</v>
+        <v>31.79</v>
       </c>
       <c r="G37">
-        <v>600</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Multi Therapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B38">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>0.72</v>
-      </c>
-      <c r="D38">
-        <v>1.34</v>
+        <v>0.49</v>
       </c>
       <c r="E38">
         <v>0.49</v>
       </c>
       <c r="F38">
-        <v>5.15</v>
+        <v>0.49</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B39">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>20.27</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>156.88</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>82</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Multi Therapist</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B40">
-        <v>16</v>
+        <v>1401</v>
       </c>
       <c r="C40">
-        <v>3.7</v>
+        <v>1.71</v>
       </c>
       <c r="D40">
-        <v>2.22</v>
+        <v>4.82</v>
       </c>
       <c r="E40">
-        <v>1.48</v>
+        <v>0.49</v>
       </c>
       <c r="F40">
-        <v>5.92</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Multi Therapist Specialist Practitioner</t>
+          <t>Occupational Therapist</t>
         </is>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>0.49</v>
+        <v>0.87</v>
+      </c>
+      <c r="D41">
+        <v>0.66</v>
       </c>
       <c r="E41">
         <v>0.49</v>
       </c>
       <c r="F41">
-        <v>0.49</v>
+        <v>1.42</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>Optometrist</t>
         </is>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="G42">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B43">
-        <v>7078</v>
+        <v>95</v>
       </c>
       <c r="C43">
-        <v>5.05</v>
+        <v>6.61</v>
       </c>
       <c r="D43">
-        <v>230.1</v>
+        <v>20</v>
       </c>
       <c r="E43">
-        <v>0.49</v>
+        <v>1.48</v>
       </c>
       <c r="F43">
-        <v>4503.12</v>
+        <v>73.69</v>
       </c>
       <c r="G43">
-        <v>869</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nursery Nurse</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>324</v>
       </c>
       <c r="C44">
-        <v>0.64</v>
+        <v>1.59</v>
       </c>
       <c r="D44">
-        <v>0.63</v>
+        <v>2.98</v>
       </c>
       <c r="E44">
         <v>0.49</v>
       </c>
       <c r="F44">
-        <v>2.18</v>
+        <v>18.01</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Occupational Therapist</t>
+          <t>Other Community Health Service - Social Care Worker</t>
         </is>
       </c>
       <c r="B45">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>2.03</v>
-      </c>
-      <c r="D45">
-        <v>20.05</v>
+        <v>2.37</v>
       </c>
       <c r="E45">
-        <v>0.99</v>
+        <v>2.37</v>
       </c>
       <c r="F45">
-        <v>51.46</v>
+        <v>2.37</v>
       </c>
       <c r="G45">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Optometrist</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B46">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="C46">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="D46">
-        <v>3.8</v>
+        <v>11.34</v>
       </c>
       <c r="E46">
         <v>0.49</v>
       </c>
       <c r="F46">
-        <v>11.75</v>
+        <v>120.08</v>
       </c>
       <c r="G46">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Paramedic Consultant</t>
         </is>
       </c>
       <c r="B47">
-        <v>375</v>
+        <v>10</v>
       </c>
       <c r="C47">
-        <v>14.48</v>
+        <v>1.08</v>
       </c>
       <c r="D47">
-        <v>63.63</v>
+        <v>1.15</v>
       </c>
       <c r="E47">
         <v>0.49</v>
       </c>
       <c r="F47">
-        <v>191.79</v>
+        <v>3.13</v>
       </c>
       <c r="G47">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B48">
-        <v>1139</v>
+        <v>194</v>
       </c>
       <c r="C48">
-        <v>3.17</v>
+        <v>1.08</v>
       </c>
       <c r="D48">
-        <v>75.84</v>
+        <v>2.26</v>
       </c>
       <c r="E48">
         <v>0.49</v>
       </c>
       <c r="F48">
-        <v>1080.75</v>
+        <v>12.77</v>
       </c>
       <c r="G48">
-        <v>224</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Social Care Worker</t>
+          <t>Patient Welfare Officer</t>
         </is>
       </c>
       <c r="B49">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D49">
-        <v>9.35</v>
+        <v>0.49</v>
       </c>
       <c r="E49">
-        <v>3.37</v>
+        <v>0.49</v>
       </c>
       <c r="F49">
-        <v>16.59</v>
+        <v>0.49</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B50">
-        <v>648</v>
+        <v>497</v>
       </c>
       <c r="C50">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="D50">
-        <v>104.22</v>
+        <v>1.4</v>
       </c>
       <c r="E50">
         <v>0.49</v>
       </c>
       <c r="F50">
-        <v>1441</v>
+        <v>7.9</v>
       </c>
       <c r="G50">
-        <v>271</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Paramedic Consultant</t>
+          <t>Physiotherapist Consultant</t>
         </is>
       </c>
       <c r="B51">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C51">
-        <v>1.38</v>
+        <v>0.72</v>
       </c>
       <c r="D51">
-        <v>3.45</v>
+        <v>0.34</v>
       </c>
       <c r="E51">
         <v>0.49</v>
       </c>
       <c r="F51">
-        <v>12.87</v>
+        <v>1.48</v>
       </c>
       <c r="G51">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Physiotherapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B52">
-        <v>622</v>
+        <v>29</v>
       </c>
       <c r="C52">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="D52">
-        <v>76.48999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E52">
         <v>0.49</v>
       </c>
       <c r="F52">
-        <v>1080.75</v>
+        <v>2.47</v>
       </c>
       <c r="G52">
-        <v>236</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Patient Welfare Officer</t>
+          <t>Practitioner</t>
         </is>
       </c>
       <c r="B53">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="C53">
-        <v>3.63</v>
+        <v>1.63</v>
       </c>
       <c r="D53">
-        <v>16.78</v>
+        <v>2.32</v>
       </c>
       <c r="E53">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="F53">
-        <v>54.04</v>
+        <v>13.86</v>
       </c>
       <c r="G53">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Pre-reg Pharmacist</t>
         </is>
       </c>
       <c r="B54">
-        <v>2366</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>2.29</v>
-      </c>
-      <c r="D54">
-        <v>365.67</v>
+        <v>0.88</v>
       </c>
       <c r="E54">
-        <v>0.49</v>
+        <v>0.88</v>
       </c>
       <c r="F54">
-        <v>9006.25</v>
+        <v>0.88</v>
       </c>
       <c r="G54">
-        <v>629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Physiotherapist Consultant</t>
+          <t>Psychotherapist</t>
         </is>
       </c>
       <c r="B55">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="C55">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="D55">
-        <v>8.41</v>
+        <v>0.99</v>
       </c>
       <c r="E55">
         <v>0.49</v>
       </c>
       <c r="F55">
-        <v>40.94</v>
+        <v>2.47</v>
       </c>
       <c r="G55">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Physiotherapist Specialist Practitioner</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="B56">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="C56">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="D56">
-        <v>10.28</v>
+        <v>1.5</v>
       </c>
       <c r="E56">
         <v>0.49</v>
       </c>
       <c r="F56">
-        <v>65.5</v>
+        <v>5.51</v>
       </c>
       <c r="G56">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Practitioner</t>
+          <t>Regional Dental Officer</t>
         </is>
       </c>
       <c r="B57">
-        <v>1513</v>
+        <v>13</v>
       </c>
       <c r="C57">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="D57">
-        <v>128.78</v>
+        <v>2.02</v>
       </c>
       <c r="E57">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="F57">
-        <v>1756.22</v>
+        <v>4.44</v>
       </c>
       <c r="G57">
-        <v>227</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pre-reg Pharmacist</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>26459</v>
       </c>
       <c r="C58">
-        <v>0.88</v>
+        <v>3.17</v>
+      </c>
+      <c r="D58">
+        <v>11.46</v>
       </c>
       <c r="E58">
-        <v>0.88</v>
+        <v>0.49</v>
       </c>
       <c r="F58">
-        <v>0.88</v>
+        <v>360.25</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>4934</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Psychotherapist</t>
+          <t>Senior House Officer</t>
         </is>
       </c>
       <c r="B59">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C59">
-        <v>3.51</v>
+        <v>1.55</v>
       </c>
       <c r="D59">
-        <v>96.45999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="E59">
         <v>0.49</v>
       </c>
       <c r="F59">
-        <v>360.25</v>
+        <v>9.01</v>
       </c>
       <c r="G59">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Radiologist</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B60">
-        <v>220</v>
+        <v>12099</v>
       </c>
       <c r="C60">
-        <v>5.15</v>
+        <v>2.12</v>
       </c>
       <c r="D60">
-        <v>20.5</v>
+        <v>17.13</v>
       </c>
       <c r="E60">
         <v>0.49</v>
       </c>
       <c r="F60">
-        <v>102.93</v>
+        <v>720.5</v>
       </c>
       <c r="G60">
-        <v>26</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Regional Dental Officer</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B61">
-        <v>39</v>
+        <v>2506</v>
       </c>
       <c r="C61">
-        <v>3.56</v>
+        <v>2.01</v>
       </c>
       <c r="D61">
-        <v>3.97</v>
+        <v>4.44</v>
       </c>
       <c r="E61">
         <v>0.49</v>
       </c>
       <c r="F61">
-        <v>11.34</v>
+        <v>51.82</v>
       </c>
       <c r="G61">
-        <v>6</v>
+        <v>704</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B62">
-        <v>110815</v>
+        <v>7</v>
       </c>
       <c r="C62">
-        <v>8.52</v>
+        <v>3.62</v>
       </c>
       <c r="D62">
-        <v>430.02</v>
+        <v>2.08</v>
       </c>
       <c r="E62">
-        <v>0.49</v>
+        <v>1.62</v>
       </c>
       <c r="F62">
-        <v>15130.5</v>
+        <v>4.56</v>
       </c>
       <c r="G62">
-        <v>8276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior House Officer</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B63">
-        <v>148</v>
+        <v>11822</v>
       </c>
       <c r="C63">
-        <v>2.81</v>
+        <v>1.99</v>
       </c>
       <c r="D63">
-        <v>15.24</v>
+        <v>5.04</v>
       </c>
       <c r="E63">
         <v>0.49</v>
       </c>
       <c r="F63">
-        <v>72.05</v>
+        <v>180.12</v>
       </c>
       <c r="G63">
-        <v>39</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B64">
-        <v>56346</v>
+        <v>138</v>
       </c>
       <c r="C64">
-        <v>5.07</v>
+        <v>1.85</v>
       </c>
       <c r="D64">
-        <v>405.39</v>
+        <v>1.58</v>
       </c>
       <c r="E64">
         <v>0.49</v>
       </c>
       <c r="F64">
-        <v>20894.5</v>
+        <v>7.58</v>
       </c>
       <c r="G64">
-        <v>7107</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Specialist Registrar</t>
         </is>
       </c>
       <c r="B65">
-        <v>12724</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>6.38</v>
-      </c>
-      <c r="D65">
-        <v>663.1</v>
+        <v>1.17</v>
       </c>
       <c r="E65">
-        <v>0.49</v>
+        <v>1.17</v>
       </c>
       <c r="F65">
-        <v>20174</v>
+        <v>1.17</v>
       </c>
       <c r="G65">
-        <v>1274</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Social Care Support Worker</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>6702</v>
       </c>
       <c r="C66">
-        <v>4.77</v>
+        <v>2.11</v>
       </c>
       <c r="D66">
-        <v>252.2</v>
+        <v>5.8</v>
       </c>
       <c r="E66">
-        <v>3.59</v>
+        <v>0.49</v>
       </c>
       <c r="F66">
-        <v>360.25</v>
+        <v>144.1</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B67">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C67">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="D67">
-        <v>5.03</v>
+        <v>5.32</v>
       </c>
       <c r="E67">
-        <v>0.49</v>
+        <v>1.43</v>
       </c>
       <c r="F67">
-        <v>11.36</v>
+        <v>19.21</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Trainee Practitioner</t>
         </is>
       </c>
       <c r="B68">
-        <v>58066</v>
+        <v>47</v>
       </c>
       <c r="C68">
-        <v>5.33</v>
+        <v>1.19</v>
       </c>
       <c r="D68">
-        <v>265.02</v>
+        <v>74.86</v>
       </c>
       <c r="E68">
         <v>0.49</v>
       </c>
       <c r="F68">
-        <v>13869.62</v>
+        <v>360.25</v>
       </c>
       <c r="G68">
-        <v>6928</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>692</v>
-      </c>
-      <c r="C69">
-        <v>5.47</v>
-      </c>
-      <c r="D69">
-        <v>21.32</v>
-      </c>
-      <c r="E69">
-        <v>0.49</v>
-      </c>
-      <c r="F69">
-        <v>168.12</v>
-      </c>
-      <c r="G69">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Specialist Registrar</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>18</v>
-      </c>
-      <c r="C70">
-        <v>1.91</v>
-      </c>
-      <c r="D70">
-        <v>118.52</v>
-      </c>
-      <c r="E70">
-        <v>0.49</v>
-      </c>
-      <c r="F70">
-        <v>360.25</v>
-      </c>
-      <c r="G70">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>34968</v>
-      </c>
-      <c r="C71">
-        <v>6.58</v>
-      </c>
-      <c r="D71">
-        <v>404.37</v>
-      </c>
-      <c r="E71">
-        <v>0.49</v>
-      </c>
-      <c r="F71">
-        <v>20894.5</v>
-      </c>
-      <c r="G71">
-        <v>3377</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>134</v>
-      </c>
-      <c r="C72">
-        <v>5.39</v>
-      </c>
-      <c r="D72">
-        <v>19.07</v>
-      </c>
-      <c r="E72">
-        <v>0.49</v>
-      </c>
-      <c r="F72">
-        <v>64.91</v>
-      </c>
-      <c r="G72">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Trainee Practitioner</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>206</v>
-      </c>
-      <c r="C73">
-        <v>1.76</v>
-      </c>
-      <c r="D73">
-        <v>123.93</v>
-      </c>
-      <c r="E73">
-        <v>0.49</v>
-      </c>
-      <c r="F73">
-        <v>1080.75</v>
-      </c>
-      <c r="G73">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -4185,25 +3911,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>64.39</v>
+        <v>13.47</v>
       </c>
       <c r="B2">
         <v>0.49</v>
       </c>
       <c r="C2">
-        <v>131851.5</v>
+        <v>1441</v>
       </c>
       <c r="D2">
-        <v>3217.39</v>
+        <v>32.75</v>
       </c>
       <c r="E2">
-        <v>54.28</v>
+        <v>11.44</v>
       </c>
       <c r="F2">
-        <v>29.12</v>
+        <v>5.92</v>
       </c>
       <c r="G2">
-        <v>115.59</v>
+        <v>21.71</v>
       </c>
     </row>
   </sheetData>
@@ -4255,25 +3981,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>64.22</v>
+        <v>13.07</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>131851.5</v>
+        <v>1441</v>
       </c>
       <c r="D2">
-        <v>3213.25</v>
+        <v>32.25</v>
       </c>
       <c r="E2">
-        <v>53.79</v>
+        <v>10.86</v>
       </c>
       <c r="F2">
-        <v>29.12</v>
+        <v>4.93</v>
       </c>
       <c r="G2">
-        <v>115.46</v>
+        <v>21.22</v>
       </c>
     </row>
   </sheetData>
@@ -4330,22 +4056,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>1899363</v>
+        <v>395521</v>
       </c>
       <c r="C2">
-        <v>51.99</v>
+        <v>11.22</v>
       </c>
       <c r="D2">
-        <v>2591.03</v>
+        <v>26.89</v>
       </c>
       <c r="E2">
         <v>0.49</v>
       </c>
       <c r="F2">
-        <v>94745.75</v>
+        <v>1441</v>
       </c>
       <c r="G2">
-        <v>23300</v>
+        <v>22086</v>
       </c>
     </row>
     <row r="3">
@@ -4355,22 +4081,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>204771</v>
+        <v>41226</v>
       </c>
       <c r="C3">
-        <v>8.41</v>
+        <v>2.57</v>
       </c>
       <c r="D3">
-        <v>518.34</v>
+        <v>6.1</v>
       </c>
       <c r="E3">
         <v>0.49</v>
       </c>
       <c r="F3">
-        <v>21615</v>
+        <v>180.12</v>
       </c>
       <c r="G3">
-        <v>15531</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="4">
@@ -4380,22 +4106,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>250608</v>
+        <v>42645</v>
       </c>
       <c r="C4">
-        <v>10.19</v>
+        <v>4.01</v>
       </c>
       <c r="D4">
-        <v>683.21</v>
+        <v>27.75</v>
       </c>
       <c r="E4">
         <v>0.49</v>
       </c>
       <c r="F4">
-        <v>34944.25</v>
+        <v>1080.75</v>
       </c>
       <c r="G4">
-        <v>15757</v>
+        <v>6434</v>
       </c>
     </row>
   </sheetData>
@@ -4452,22 +4178,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>1899363</v>
+        <v>395521</v>
       </c>
       <c r="C2">
-        <v>51.99</v>
+        <v>11.22</v>
       </c>
       <c r="D2">
-        <v>2591.03</v>
+        <v>26.89</v>
       </c>
       <c r="E2">
         <v>0.49</v>
       </c>
       <c r="F2">
-        <v>94745.75</v>
+        <v>1441</v>
       </c>
       <c r="G2">
-        <v>23300</v>
+        <v>22086</v>
       </c>
     </row>
     <row r="3">
@@ -4492,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>61</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="4">
@@ -4502,22 +4228,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>204771</v>
+        <v>41226</v>
       </c>
       <c r="C4">
-        <v>8.41</v>
+        <v>2.57</v>
       </c>
       <c r="D4">
-        <v>518.34</v>
+        <v>6.1</v>
       </c>
       <c r="E4">
         <v>0.49</v>
       </c>
       <c r="F4">
-        <v>21615</v>
+        <v>180.12</v>
       </c>
       <c r="G4">
-        <v>15531</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="5">
@@ -4527,22 +4253,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>250608</v>
+        <v>42645</v>
       </c>
       <c r="C5">
-        <v>10.19</v>
+        <v>4.01</v>
       </c>
       <c r="D5">
-        <v>683.21</v>
+        <v>27.75</v>
       </c>
       <c r="E5">
         <v>0.49</v>
       </c>
       <c r="F5">
-        <v>34944.25</v>
+        <v>1080.75</v>
       </c>
       <c r="G5">
-        <v>15757</v>
+        <v>6434</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP.xlsx
@@ -398,7 +398,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>14.37</v>
+        <v>15.21</v>
       </c>
       <c r="B2">
         <v>0.5</v>
@@ -407,16 +407,16 @@
         <v>311.23</v>
       </c>
       <c r="D2">
-        <v>17.98</v>
+        <v>18.75</v>
       </c>
       <c r="E2">
-        <v>11.78</v>
+        <v>12.51</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G2">
-        <v>22.02</v>
+        <v>23.52</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -764,325 +764,350 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>2076</v>
+        <v>32874</v>
       </c>
       <c r="C11">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="D11">
-        <v>3.68</v>
+        <v>4.64</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>39.78</v>
+        <v>71.27</v>
       </c>
       <c r="G11">
-        <v>643</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B12">
-        <v>439</v>
+        <v>2076</v>
       </c>
       <c r="C12">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="D12">
-        <v>2.36</v>
+        <v>3.68</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>18.73</v>
+        <v>39.78</v>
       </c>
       <c r="G12">
-        <v>231</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B13">
-        <v>6483</v>
+        <v>439</v>
       </c>
       <c r="C13">
-        <v>3.24</v>
+        <v>1.11</v>
       </c>
       <c r="D13">
-        <v>6.86</v>
+        <v>2.36</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>80.65000000000001</v>
+        <v>18.73</v>
       </c>
       <c r="G13">
-        <v>1182</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B14">
-        <v>524</v>
+        <v>6483</v>
       </c>
       <c r="C14">
-        <v>1.5</v>
+        <v>3.24</v>
       </c>
       <c r="D14">
-        <v>1.39</v>
+        <v>6.86</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>8.01</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G14">
-        <v>192</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B15">
-        <v>30056</v>
+        <v>524</v>
       </c>
       <c r="C15">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="D15">
-        <v>3.58</v>
+        <v>1.39</v>
       </c>
       <c r="E15">
         <v>0.5</v>
       </c>
       <c r="F15">
-        <v>79.40000000000001</v>
+        <v>8.01</v>
       </c>
       <c r="G15">
-        <v>8078</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B16">
-        <v>116</v>
+        <v>30056</v>
       </c>
       <c r="C16">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="D16">
-        <v>1.07</v>
+        <v>3.58</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>5.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G16">
-        <v>63</v>
+        <v>8078</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B17">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="C17">
-        <v>2.69</v>
+        <v>1.01</v>
       </c>
       <c r="D17">
-        <v>3.18</v>
+        <v>1.07</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>15.01</v>
+        <v>5.5</v>
       </c>
       <c r="G17">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B18">
-        <v>16010</v>
+        <v>162</v>
       </c>
       <c r="C18">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="D18">
-        <v>5.53</v>
+        <v>3.18</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>162.05</v>
+        <v>15.01</v>
       </c>
       <c r="G18">
-        <v>3943</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B19">
-        <v>82</v>
+        <v>16010</v>
       </c>
       <c r="C19">
-        <v>0.82</v>
+        <v>2.35</v>
       </c>
       <c r="D19">
-        <v>1.28</v>
+        <v>5.53</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>7.69</v>
+        <v>162.05</v>
       </c>
       <c r="G19">
-        <v>57</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B20">
-        <v>3941</v>
+        <v>82</v>
       </c>
       <c r="C20">
-        <v>1.91</v>
+        <v>0.82</v>
       </c>
       <c r="D20">
-        <v>3.95</v>
+        <v>1.28</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>77.04000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="G20">
-        <v>1155</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B21">
-        <v>9911</v>
+        <v>3941</v>
       </c>
       <c r="C21">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="D21">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>62.61</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G21">
-        <v>2591</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>9911</v>
       </c>
       <c r="C22">
-        <v>3.53</v>
+        <v>2.17</v>
       </c>
       <c r="D22">
-        <v>1.92</v>
+        <v>3.94</v>
       </c>
       <c r="E22">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="F22">
-        <v>4.36</v>
+        <v>62.61</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>3.53</v>
+      </c>
+      <c r="D23">
+        <v>1.92</v>
+      </c>
+      <c r="E23">
+        <v>1.65</v>
+      </c>
+      <c r="F23">
+        <v>4.36</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>638</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>1.82</v>
       </c>
-      <c r="D23">
+      <c r="D24">
         <v>3.34</v>
       </c>
-      <c r="E23">
-        <v>0.5</v>
-      </c>
-      <c r="F23">
+      <c r="E24">
+        <v>0.5</v>
+      </c>
+      <c r="F24">
         <v>34.6</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>198</v>
       </c>
     </row>
@@ -1093,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1361,350 +1386,375 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>32874</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>71.27</v>
       </c>
       <c r="G11">
-        <v>723</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B12">
-        <v>2076</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>39.78</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>643</v>
+        <v>631</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B13">
-        <v>439</v>
+        <v>2076</v>
       </c>
       <c r="C13">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="D13">
-        <v>2.36</v>
+        <v>3.68</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>18.73</v>
+        <v>39.78</v>
       </c>
       <c r="G13">
-        <v>231</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B14">
-        <v>6483</v>
+        <v>439</v>
       </c>
       <c r="C14">
-        <v>3.24</v>
+        <v>1.11</v>
       </c>
       <c r="D14">
-        <v>6.86</v>
+        <v>2.36</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>80.65000000000001</v>
+        <v>18.73</v>
       </c>
       <c r="G14">
-        <v>1182</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>524</v>
+        <v>6483</v>
       </c>
       <c r="C15">
-        <v>1.5</v>
+        <v>3.24</v>
       </c>
       <c r="D15">
-        <v>1.39</v>
+        <v>6.86</v>
       </c>
       <c r="E15">
         <v>0.5</v>
       </c>
       <c r="F15">
-        <v>8.01</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G15">
-        <v>192</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B16">
-        <v>30056</v>
+        <v>524</v>
       </c>
       <c r="C16">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="D16">
-        <v>3.58</v>
+        <v>1.39</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>79.40000000000001</v>
+        <v>8.01</v>
       </c>
       <c r="G16">
-        <v>8078</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B17">
-        <v>116</v>
+        <v>30056</v>
       </c>
       <c r="C17">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="D17">
-        <v>1.07</v>
+        <v>3.58</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>5.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17">
-        <v>63</v>
+        <v>8078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B18">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="C18">
-        <v>2.69</v>
+        <v>1.01</v>
       </c>
       <c r="D18">
-        <v>3.18</v>
+        <v>1.07</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>15.01</v>
+        <v>5.5</v>
       </c>
       <c r="G18">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B19">
-        <v>16010</v>
+        <v>162</v>
       </c>
       <c r="C19">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="D19">
-        <v>5.53</v>
+        <v>3.18</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>162.05</v>
+        <v>15.01</v>
       </c>
       <c r="G19">
-        <v>3943</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B20">
-        <v>82</v>
+        <v>16010</v>
       </c>
       <c r="C20">
-        <v>0.82</v>
+        <v>2.35</v>
       </c>
       <c r="D20">
-        <v>1.28</v>
+        <v>5.53</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>7.69</v>
+        <v>162.05</v>
       </c>
       <c r="G20">
-        <v>57</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B21">
-        <v>3941</v>
+        <v>82</v>
       </c>
       <c r="C21">
-        <v>1.91</v>
+        <v>0.82</v>
       </c>
       <c r="D21">
-        <v>3.95</v>
+        <v>1.28</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>77.04000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="G21">
-        <v>1155</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>9911</v>
+        <v>3941</v>
       </c>
       <c r="C22">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="D22">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>62.61</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>2591</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>9911</v>
       </c>
       <c r="C23">
-        <v>3.53</v>
+        <v>2.17</v>
       </c>
       <c r="D23">
-        <v>1.92</v>
+        <v>3.94</v>
       </c>
       <c r="E23">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="F23">
-        <v>4.36</v>
+        <v>62.61</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>3.53</v>
+      </c>
+      <c r="D24">
+        <v>1.92</v>
+      </c>
+      <c r="E24">
+        <v>1.65</v>
+      </c>
+      <c r="F24">
+        <v>4.36</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>638</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>1.82</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>3.34</v>
       </c>
-      <c r="E24">
-        <v>0.5</v>
-      </c>
-      <c r="F24">
+      <c r="E25">
+        <v>0.5</v>
+      </c>
+      <c r="F25">
         <v>34.6</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>198</v>
       </c>
     </row>
@@ -1715,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1828,6 +1878,31 @@
       </c>
       <c r="G4">
         <v>8906</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>32874</v>
+      </c>
+      <c r="C5">
+        <v>2.32</v>
+      </c>
+      <c r="D5">
+        <v>4.64</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>71.27</v>
+      </c>
+      <c r="G5">
+        <v>8334</v>
       </c>
     </row>
   </sheetData>
@@ -1837,7 +1912,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1924,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>723</v>
+        <v>631</v>
       </c>
     </row>
     <row r="4">
@@ -1975,6 +2050,31 @@
       </c>
       <c r="G5">
         <v>8906</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>32874</v>
+      </c>
+      <c r="C6">
+        <v>2.32</v>
+      </c>
+      <c r="D6">
+        <v>4.64</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>71.27</v>
+      </c>
+      <c r="G6">
+        <v>8334</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP.xlsx
@@ -468,25 +468,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>13.22</v>
+        <v>14.81</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>266.38</v>
+        <v>311.23</v>
       </c>
       <c r="D2">
-        <v>16.87</v>
+        <v>18.72</v>
       </c>
       <c r="E2">
-        <v>10.86</v>
+        <v>12.01</v>
       </c>
       <c r="F2">
-        <v>4.93</v>
+        <v>5.75</v>
       </c>
       <c r="G2">
-        <v>20.73</v>
+        <v>23.02</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>45115</v>
+        <v>45114</v>
       </c>
       <c r="C4">
         <v>2.63</v>
@@ -608,7 +608,7 @@
         <v>186.45</v>
       </c>
       <c r="G4">
-        <v>9887</v>
+        <v>9886</v>
       </c>
     </row>
     <row r="5">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>343407</v>
+        <v>343392</v>
       </c>
       <c r="C7">
         <v>9.44</v>
@@ -683,7 +683,7 @@
         <v>166.11</v>
       </c>
       <c r="G7">
-        <v>22581</v>
+        <v>22580</v>
       </c>
     </row>
     <row r="8">
@@ -789,325 +789,350 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B12">
-        <v>2076</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>39.78</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>643</v>
+        <v>23117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B13">
-        <v>439</v>
+        <v>2076</v>
       </c>
       <c r="C13">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="D13">
-        <v>2.36</v>
+        <v>3.68</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>18.73</v>
+        <v>39.78</v>
       </c>
       <c r="G13">
-        <v>231</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B14">
-        <v>6483</v>
+        <v>439</v>
       </c>
       <c r="C14">
-        <v>3.24</v>
+        <v>1.11</v>
       </c>
       <c r="D14">
-        <v>6.86</v>
+        <v>2.36</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>80.65000000000001</v>
+        <v>18.73</v>
       </c>
       <c r="G14">
-        <v>1182</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>524</v>
+        <v>6483</v>
       </c>
       <c r="C15">
-        <v>1.5</v>
+        <v>3.24</v>
       </c>
       <c r="D15">
-        <v>1.39</v>
+        <v>6.86</v>
       </c>
       <c r="E15">
         <v>0.5</v>
       </c>
       <c r="F15">
-        <v>8.01</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G15">
-        <v>192</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B16">
-        <v>30056</v>
+        <v>524</v>
       </c>
       <c r="C16">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="D16">
-        <v>3.58</v>
+        <v>1.39</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>79.40000000000001</v>
+        <v>8.01</v>
       </c>
       <c r="G16">
-        <v>8078</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B17">
-        <v>116</v>
+        <v>30056</v>
       </c>
       <c r="C17">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="D17">
-        <v>1.07</v>
+        <v>3.58</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>5.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17">
-        <v>63</v>
+        <v>8078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B18">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="C18">
-        <v>2.69</v>
+        <v>1.01</v>
       </c>
       <c r="D18">
-        <v>3.18</v>
+        <v>1.07</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>15.01</v>
+        <v>5.5</v>
       </c>
       <c r="G18">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B19">
-        <v>16010</v>
+        <v>162</v>
       </c>
       <c r="C19">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="D19">
-        <v>5.53</v>
+        <v>3.18</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>162.05</v>
+        <v>15.01</v>
       </c>
       <c r="G19">
-        <v>3943</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B20">
-        <v>82</v>
+        <v>16010</v>
       </c>
       <c r="C20">
-        <v>0.82</v>
+        <v>2.35</v>
       </c>
       <c r="D20">
-        <v>1.28</v>
+        <v>5.53</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>7.69</v>
+        <v>162.05</v>
       </c>
       <c r="G20">
-        <v>57</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B21">
-        <v>3941</v>
+        <v>82</v>
       </c>
       <c r="C21">
-        <v>1.91</v>
+        <v>0.82</v>
       </c>
       <c r="D21">
-        <v>3.95</v>
+        <v>1.28</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>77.04000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="G21">
-        <v>1155</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>9911</v>
+        <v>3941</v>
       </c>
       <c r="C22">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="D22">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>62.61</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>2591</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>9911</v>
       </c>
       <c r="C23">
-        <v>3.53</v>
+        <v>2.17</v>
       </c>
       <c r="D23">
-        <v>1.92</v>
+        <v>3.94</v>
       </c>
       <c r="E23">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="F23">
-        <v>4.36</v>
+        <v>62.61</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>3.53</v>
+      </c>
+      <c r="D24">
+        <v>1.92</v>
+      </c>
+      <c r="E24">
+        <v>1.65</v>
+      </c>
+      <c r="F24">
+        <v>4.36</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>638</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>1.82</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>3.34</v>
       </c>
-      <c r="E24">
-        <v>0.5</v>
-      </c>
-      <c r="F24">
+      <c r="E25">
+        <v>0.5</v>
+      </c>
+      <c r="F25">
         <v>34.6</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>198</v>
       </c>
     </row>
@@ -1215,7 +1240,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>45115</v>
+        <v>45114</v>
       </c>
       <c r="C4">
         <v>2.63</v>
@@ -1230,7 +1255,7 @@
         <v>186.45</v>
       </c>
       <c r="G4">
-        <v>9887</v>
+        <v>9886</v>
       </c>
     </row>
     <row r="5">
@@ -1290,7 +1315,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>343407</v>
+        <v>343392</v>
       </c>
       <c r="C7">
         <v>9.44</v>
@@ -1305,7 +1330,7 @@
         <v>166.11</v>
       </c>
       <c r="G7">
-        <v>22581</v>
+        <v>22580</v>
       </c>
     </row>
     <row r="8">
@@ -1430,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>631</v>
+        <v>732</v>
       </c>
     </row>
     <row r="13">
@@ -1812,7 +1837,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>418578</v>
+        <v>418562</v>
       </c>
       <c r="C2">
         <v>11.39</v>
@@ -1827,7 +1852,7 @@
         <v>227.56</v>
       </c>
       <c r="G2">
-        <v>22825</v>
+        <v>22824</v>
       </c>
     </row>
     <row r="3">
@@ -1959,7 +1984,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>418578</v>
+        <v>418562</v>
       </c>
       <c r="C2">
         <v>11.39</v>
@@ -1974,7 +1999,7 @@
         <v>227.56</v>
       </c>
       <c r="G2">
-        <v>22825</v>
+        <v>22824</v>
       </c>
     </row>
     <row r="3">
@@ -1999,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>631</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4">

--- a/OMOP Analysis/Results/Output_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP.xlsx
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -416,7 +416,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -426,22 +426,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>7905</v>
+        <v>11862</v>
       </c>
       <c r="C3">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="D3">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>58.91</v>
+        <v>59.63</v>
       </c>
       <c r="G3">
-        <v>2343</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
@@ -451,22 +451,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>30621</v>
+        <v>42901</v>
       </c>
       <c r="C4">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="D4">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>119.93</v>
+        <v>186.45</v>
       </c>
       <c r="G4">
-        <v>6790</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>17534</v>
+        <v>22347</v>
       </c>
       <c r="C5">
-        <v>4.76</v>
+        <v>5.27</v>
       </c>
       <c r="D5">
-        <v>9.57</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -491,7 +491,7 @@
         <v>77.48</v>
       </c>
       <c r="G5">
-        <v>2269</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C6">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="D6">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>3.88</v>
+        <v>14.05</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>227475</v>
+        <v>325922</v>
       </c>
       <c r="C7">
-        <v>9.32</v>
+        <v>11.23</v>
       </c>
       <c r="D7">
-        <v>12.71</v>
+        <v>12.66</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -541,7 +541,7 @@
         <v>166.11</v>
       </c>
       <c r="G7">
-        <v>16314</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C8">
-        <v>4.58</v>
+        <v>3.38</v>
       </c>
       <c r="D8">
-        <v>7.85</v>
+        <v>5.11</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
-        <v>22.83</v>
+        <v>19.48</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>26683</v>
+        <v>36677</v>
       </c>
       <c r="C9">
-        <v>4.64</v>
+        <v>5.05</v>
       </c>
       <c r="D9">
-        <v>11.11</v>
+        <v>9.73</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G9">
-        <v>3723</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>0.5</v>
@@ -616,7 +616,7 @@
         <v>0.5</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -626,22 +626,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>21569</v>
+        <v>31006</v>
       </c>
       <c r="C11">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="D11">
-        <v>5.45</v>
+        <v>5.07</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>69.56999999999999</v>
+        <v>71.27</v>
       </c>
       <c r="G11">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>16856</v>
+        <v>22119</v>
       </c>
     </row>
     <row r="13">
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>1369</v>
+        <v>1916</v>
       </c>
       <c r="C13">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="D13">
-        <v>4.54</v>
+        <v>4.21</v>
       </c>
       <c r="E13">
         <v>0.5</v>
@@ -691,7 +691,7 @@
         <v>44.54</v>
       </c>
       <c r="G13">
-        <v>421</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14">
@@ -701,22 +701,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>319</v>
+        <v>426</v>
       </c>
       <c r="C14">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="D14">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>18.73</v>
+        <v>22.14</v>
       </c>
       <c r="G14">
-        <v>169</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="B15">
-        <v>5049</v>
+        <v>6094</v>
       </c>
       <c r="C15">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="D15">
-        <v>7.63</v>
+        <v>6.95</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -741,7 +741,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="G15">
-        <v>841</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="16">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>306</v>
+        <v>468</v>
       </c>
       <c r="C16">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="D16">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>22</v>
+        <v>23.95</v>
       </c>
       <c r="G16">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>19642</v>
+        <v>28368</v>
       </c>
       <c r="C17">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="E17">
         <v>0.5</v>
@@ -791,7 +791,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="G17">
-        <v>5299</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="18">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C18">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="D18">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="E18">
         <v>0.5</v>
@@ -816,7 +816,7 @@
         <v>5.5</v>
       </c>
       <c r="G18">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -826,22 +826,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="C19">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="D19">
-        <v>2.34</v>
+        <v>3.19</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>9.51</v>
+        <v>15.01</v>
       </c>
       <c r="G19">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -851,22 +851,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>10157</v>
+        <v>15197</v>
       </c>
       <c r="C20">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="D20">
-        <v>5.73</v>
+        <v>5.96</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>98.06999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G20">
-        <v>2605</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="21">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="D21">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>7.69</v>
+        <v>8.82</v>
       </c>
       <c r="G21">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -901,22 +901,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>2708</v>
+        <v>3848</v>
       </c>
       <c r="C22">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="D22">
-        <v>4.19</v>
+        <v>5.01</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>49.81</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>781</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23">
@@ -926,22 +926,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>6704</v>
+        <v>9644</v>
       </c>
       <c r="C23">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="D23">
-        <v>4.39</v>
+        <v>5.83</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>46.59</v>
+        <v>146.1</v>
       </c>
       <c r="G23">
-        <v>1765</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="24">
@@ -976,22 +976,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>488</v>
+        <v>593</v>
       </c>
       <c r="C25">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="D25">
-        <v>4.04</v>
+        <v>4.1</v>
       </c>
       <c r="E25">
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>31.76</v>
+        <v>34.6</v>
       </c>
       <c r="G25">
-        <v>144</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -1063,7 +1063,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>7905</v>
+        <v>11862</v>
       </c>
       <c r="C3">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="D3">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>58.91</v>
+        <v>59.63</v>
       </c>
       <c r="G3">
-        <v>2343</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>30621</v>
+        <v>42901</v>
       </c>
       <c r="C4">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="D4">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>119.93</v>
+        <v>186.45</v>
       </c>
       <c r="G4">
-        <v>6790</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>17534</v>
+        <v>22347</v>
       </c>
       <c r="C5">
-        <v>4.76</v>
+        <v>5.27</v>
       </c>
       <c r="D5">
-        <v>9.57</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -1138,7 +1138,7 @@
         <v>77.48</v>
       </c>
       <c r="G5">
-        <v>2269</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C6">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="D6">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>3.88</v>
+        <v>14.05</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>227475</v>
+        <v>325922</v>
       </c>
       <c r="C7">
-        <v>9.32</v>
+        <v>11.23</v>
       </c>
       <c r="D7">
-        <v>12.71</v>
+        <v>12.66</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -1188,7 +1188,7 @@
         <v>166.11</v>
       </c>
       <c r="G7">
-        <v>16314</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C8">
-        <v>4.58</v>
+        <v>3.38</v>
       </c>
       <c r="D8">
-        <v>7.85</v>
+        <v>5.11</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
-        <v>22.83</v>
+        <v>19.48</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>26683</v>
+        <v>36677</v>
       </c>
       <c r="C9">
-        <v>4.64</v>
+        <v>5.05</v>
       </c>
       <c r="D9">
-        <v>11.11</v>
+        <v>9.73</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G9">
-        <v>3723</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>0.5</v>
@@ -1263,7 +1263,7 @@
         <v>0.5</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>21569</v>
+        <v>31006</v>
       </c>
       <c r="C11">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="D11">
-        <v>5.45</v>
+        <v>5.07</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>69.56999999999999</v>
+        <v>71.27</v>
       </c>
       <c r="G11">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>727</v>
+        <v>621</v>
       </c>
     </row>
     <row r="13">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>1369</v>
+        <v>1916</v>
       </c>
       <c r="C13">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="D13">
-        <v>4.54</v>
+        <v>4.21</v>
       </c>
       <c r="E13">
         <v>0.5</v>
@@ -1338,7 +1338,7 @@
         <v>44.54</v>
       </c>
       <c r="G13">
-        <v>421</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>319</v>
+        <v>426</v>
       </c>
       <c r="C14">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="D14">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>18.73</v>
+        <v>22.14</v>
       </c>
       <c r="G14">
-        <v>169</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B15">
-        <v>5049</v>
+        <v>6094</v>
       </c>
       <c r="C15">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="D15">
-        <v>7.63</v>
+        <v>6.95</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -1388,7 +1388,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="G15">
-        <v>841</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="16">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>306</v>
+        <v>468</v>
       </c>
       <c r="C16">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="D16">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>22</v>
+        <v>23.95</v>
       </c>
       <c r="G16">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>19642</v>
+        <v>28368</v>
       </c>
       <c r="C17">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="E17">
         <v>0.5</v>
@@ -1438,7 +1438,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="G17">
-        <v>5299</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="18">
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C18">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="D18">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="E18">
         <v>0.5</v>
@@ -1463,7 +1463,7 @@
         <v>5.5</v>
       </c>
       <c r="G18">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="C19">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="D19">
-        <v>2.34</v>
+        <v>3.19</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>9.51</v>
+        <v>15.01</v>
       </c>
       <c r="G19">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>10157</v>
+        <v>15197</v>
       </c>
       <c r="C20">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="D20">
-        <v>5.73</v>
+        <v>5.96</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>98.06999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G20">
-        <v>2605</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="21">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="D21">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>7.69</v>
+        <v>8.82</v>
       </c>
       <c r="G21">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>2708</v>
+        <v>3848</v>
       </c>
       <c r="C22">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="D22">
-        <v>4.19</v>
+        <v>5.01</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>49.81</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>781</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>6704</v>
+        <v>9644</v>
       </c>
       <c r="C23">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="D23">
-        <v>4.39</v>
+        <v>5.83</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>46.59</v>
+        <v>146.1</v>
       </c>
       <c r="G23">
-        <v>1765</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="24">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>488</v>
+        <v>593</v>
       </c>
       <c r="C25">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="D25">
-        <v>4.04</v>
+        <v>4.1</v>
       </c>
       <c r="E25">
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>31.76</v>
+        <v>34.6</v>
       </c>
       <c r="G25">
-        <v>144</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1695,22 +1695,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>277738</v>
+        <v>397191</v>
       </c>
       <c r="C2">
-        <v>11.25</v>
+        <v>13.57</v>
       </c>
       <c r="D2">
-        <v>14.67</v>
+        <v>14.66</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>207.16</v>
+        <v>227.56</v>
       </c>
       <c r="G2">
-        <v>16544</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
@@ -1720,22 +1720,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>28892</v>
+        <v>42557</v>
       </c>
       <c r="C3">
-        <v>2.58</v>
+        <v>3.02</v>
       </c>
       <c r="D3">
-        <v>5.56</v>
+        <v>6.14</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>98.56999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G3">
-        <v>6564</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="4">
@@ -1745,22 +1745,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>50649</v>
+        <v>67002</v>
       </c>
       <c r="C4">
-        <v>4.97</v>
+        <v>5.37</v>
       </c>
       <c r="D4">
-        <v>10.83</v>
+        <v>9.93</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G4">
-        <v>6458</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="5">
@@ -1770,22 +1770,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>21569</v>
+        <v>31006</v>
       </c>
       <c r="C5">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="D5">
-        <v>5.45</v>
+        <v>5.07</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>69.56999999999999</v>
+        <v>71.27</v>
       </c>
       <c r="G5">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
   </sheetData>
@@ -1842,22 +1842,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>277738</v>
+        <v>397191</v>
       </c>
       <c r="C2">
-        <v>11.25</v>
+        <v>13.57</v>
       </c>
       <c r="D2">
-        <v>14.67</v>
+        <v>14.66</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>207.16</v>
+        <v>227.56</v>
       </c>
       <c r="G2">
-        <v>16544</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>727</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4">
@@ -1892,22 +1892,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>28892</v>
+        <v>42557</v>
       </c>
       <c r="C4">
-        <v>2.58</v>
+        <v>3.02</v>
       </c>
       <c r="D4">
-        <v>5.56</v>
+        <v>6.14</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>98.56999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G4">
-        <v>6564</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="5">
@@ -1917,22 +1917,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>50649</v>
+        <v>67002</v>
       </c>
       <c r="C5">
-        <v>4.97</v>
+        <v>5.37</v>
       </c>
       <c r="D5">
-        <v>10.83</v>
+        <v>9.93</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G5">
-        <v>6458</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="6">
@@ -1942,22 +1942,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>21569</v>
+        <v>31006</v>
       </c>
       <c r="C6">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="D6">
-        <v>5.45</v>
+        <v>5.07</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>69.56999999999999</v>
+        <v>71.27</v>
       </c>
       <c r="G6">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,19 +401,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="D2">
-        <v>0.71</v>
+        <v>1.18</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -422,576 +422,821 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Case Manager / Care Coordinator</t>
         </is>
       </c>
       <c r="B3">
-        <v>11862</v>
+        <v>487622</v>
       </c>
       <c r="C3">
-        <v>2.28</v>
+        <v>30.3</v>
       </c>
       <c r="D3">
-        <v>4.29</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>59.63</v>
+        <v>1027.27</v>
       </c>
       <c r="G3">
-        <v>3427</v>
+        <v>11466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B4">
-        <v>42901</v>
+        <v>50618</v>
       </c>
       <c r="C4">
-        <v>2.94</v>
+        <v>9.75</v>
       </c>
       <c r="D4">
-        <v>5.5</v>
+        <v>18.62</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>186.45</v>
+        <v>247.52</v>
       </c>
       <c r="G4">
-        <v>9405</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B5">
-        <v>22347</v>
+        <v>212202</v>
       </c>
       <c r="C5">
-        <v>5.27</v>
+        <v>14.56</v>
       </c>
       <c r="D5">
-        <v>9.630000000000001</v>
+        <v>25.92</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>77.48</v>
+        <v>557.4400000000001</v>
       </c>
       <c r="G5">
-        <v>2879</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>118532</v>
       </c>
       <c r="C6">
-        <v>2.22</v>
+        <v>27.97</v>
       </c>
       <c r="D6">
-        <v>3.9</v>
+        <v>69.36</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>14.05</v>
+        <v>1891.94</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B7">
-        <v>325922</v>
+        <v>383</v>
       </c>
       <c r="C7">
-        <v>11.23</v>
+        <v>9.43</v>
       </c>
       <c r="D7">
-        <v>12.66</v>
+        <v>16.39</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>166.11</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="G7">
-        <v>21658</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B8">
-        <v>51</v>
+        <v>909484</v>
       </c>
       <c r="C8">
-        <v>3.38</v>
+        <v>31.32</v>
       </c>
       <c r="D8">
-        <v>5.11</v>
+        <v>40.3</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>19.48</v>
+        <v>704.14</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>Health Information Technician</t>
         </is>
       </c>
       <c r="B9">
-        <v>36677</v>
+        <v>75271</v>
       </c>
       <c r="C9">
-        <v>5.05</v>
+        <v>22.06</v>
       </c>
       <c r="D9">
-        <v>9.73</v>
+        <v>37.62</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>112.76</v>
+        <v>319.59</v>
       </c>
       <c r="G9">
-        <v>4954</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>8.74</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>13.13</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>48.7</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B11">
-        <v>31006</v>
+        <v>120759</v>
       </c>
       <c r="C11">
-        <v>2.62</v>
+        <v>16.63</v>
       </c>
       <c r="D11">
-        <v>5.07</v>
+        <v>34.91</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>71.27</v>
+        <v>476.31</v>
       </c>
       <c r="G11">
-        <v>7891</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>22119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B13">
-        <v>1916</v>
+        <v>87733</v>
       </c>
       <c r="C13">
-        <v>2.01</v>
+        <v>7.42</v>
       </c>
       <c r="D13">
-        <v>4.21</v>
+        <v>16.56</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>44.54</v>
+        <v>419.65</v>
       </c>
       <c r="G13">
-        <v>616</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B14">
-        <v>426</v>
+        <v>9972</v>
       </c>
       <c r="C14">
-        <v>1.49</v>
+        <v>10.47</v>
       </c>
       <c r="D14">
-        <v>2.95</v>
+        <v>20.18</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>22.14</v>
+        <v>186.51</v>
       </c>
       <c r="G14">
-        <v>220</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Other Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>6094</v>
+        <v>831207</v>
       </c>
       <c r="C15">
-        <v>3.58</v>
+        <v>42.9</v>
       </c>
       <c r="D15">
-        <v>6.95</v>
+        <v>93.41</v>
       </c>
       <c r="E15">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F15">
-        <v>80.65000000000001</v>
+        <v>2557.75</v>
       </c>
       <c r="G15">
-        <v>1125</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B16">
-        <v>468</v>
+        <v>2150</v>
       </c>
       <c r="C16">
-        <v>1.73</v>
+        <v>7.5</v>
       </c>
       <c r="D16">
-        <v>2.8</v>
+        <v>18.93</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>23.95</v>
+        <v>114.79</v>
       </c>
       <c r="G16">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="B17">
-        <v>28368</v>
+        <v>14131</v>
       </c>
       <c r="C17">
-        <v>2.43</v>
+        <v>4.06</v>
       </c>
       <c r="D17">
-        <v>4.05</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>79.40000000000001</v>
+        <v>121.75</v>
       </c>
       <c r="G17">
-        <v>7644</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B18">
-        <v>112</v>
+        <v>19394</v>
       </c>
       <c r="C18">
-        <v>1.08</v>
+        <v>11.4</v>
       </c>
       <c r="D18">
-        <v>1.16</v>
+        <v>23.57</v>
       </c>
       <c r="E18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>5.5</v>
+        <v>267.26</v>
       </c>
       <c r="G18">
-        <v>61</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Phlebotomist</t>
         </is>
       </c>
       <c r="B19">
-        <v>141</v>
+        <v>17886</v>
       </c>
       <c r="C19">
-        <v>2.9</v>
+        <v>6.11</v>
       </c>
       <c r="D19">
-        <v>3.19</v>
+        <v>12.76</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>15.01</v>
+        <v>178.28</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B20">
-        <v>15197</v>
+        <v>1083</v>
       </c>
       <c r="C20">
-        <v>2.67</v>
+        <v>3.99</v>
       </c>
       <c r="D20">
-        <v>5.96</v>
+        <v>7.15</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>162.05</v>
+        <v>52.18</v>
       </c>
       <c r="G20">
-        <v>3731</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B21">
-        <v>75</v>
+        <v>356370</v>
       </c>
       <c r="C21">
-        <v>0.9</v>
+        <v>30.5</v>
       </c>
       <c r="D21">
-        <v>1.51</v>
+        <v>55.1</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F21">
-        <v>8.82</v>
+        <v>741.66</v>
       </c>
       <c r="G21">
-        <v>51</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Physician Office Based Coding Specialist</t>
         </is>
       </c>
       <c r="B22">
-        <v>3848</v>
+        <v>11740</v>
       </c>
       <c r="C22">
-        <v>2.2</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D22">
-        <v>5.01</v>
+        <v>21.27</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>77.04000000000001</v>
+        <v>213.38</v>
       </c>
       <c r="G22">
-        <v>1110</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B23">
-        <v>9644</v>
+        <v>807</v>
       </c>
       <c r="C23">
-        <v>2.48</v>
+        <v>7.81</v>
       </c>
       <c r="D23">
-        <v>5.83</v>
+        <v>7.41</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>146.1</v>
+        <v>42.69</v>
       </c>
       <c r="G23">
-        <v>2502</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>359</v>
       </c>
       <c r="C24">
-        <v>3.53</v>
+        <v>7.37</v>
       </c>
       <c r="D24">
-        <v>1.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E24">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="F24">
-        <v>4.36</v>
+        <v>46.03</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Radiography Technologist</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>52</v>
+      </c>
+      <c r="C25">
+        <v>4.21</v>
+      </c>
+      <c r="D25">
+        <v>2.33</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>6.95</v>
+      </c>
+      <c r="G25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Registered Community Health Nurse</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>72305</v>
+      </c>
+      <c r="C26">
+        <v>12.72</v>
+      </c>
+      <c r="D26">
+        <v>31.22</v>
+      </c>
+      <c r="E26">
+        <v>0.5</v>
+      </c>
+      <c r="F26">
+        <v>741.91</v>
+      </c>
+      <c r="G26">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Registered Dietitian</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>364</v>
+      </c>
+      <c r="C27">
+        <v>4.38</v>
+      </c>
+      <c r="D27">
+        <v>17.64</v>
+      </c>
+      <c r="E27">
+        <v>0.5</v>
+      </c>
+      <c r="F27">
+        <v>125.28</v>
+      </c>
+      <c r="G27">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Registered General Practice Nurse</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>37632</v>
+      </c>
+      <c r="C28">
+        <v>21.52</v>
+      </c>
+      <c r="D28">
+        <v>46.64</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>644.89</v>
+      </c>
+      <c r="G28">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Registered Nurse</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>48308</v>
+      </c>
+      <c r="C29">
+        <v>12.42</v>
+      </c>
+      <c r="D29">
+        <v>22.25</v>
+      </c>
+      <c r="E29">
+        <v>0.5</v>
+      </c>
+      <c r="F29">
+        <v>332.78</v>
+      </c>
+      <c r="G29">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Registered Record Administrator</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>325580</v>
+      </c>
+      <c r="C30">
+        <v>16.69</v>
+      </c>
+      <c r="D30">
+        <v>35.01</v>
+      </c>
+      <c r="E30">
+        <v>0.5</v>
+      </c>
+      <c r="F30">
+        <v>519.47</v>
+      </c>
+      <c r="G30">
+        <v>14045</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <v>8.06</v>
+      </c>
+      <c r="D31">
+        <v>6.54</v>
+      </c>
+      <c r="E31">
+        <v>1.65</v>
+      </c>
+      <c r="F31">
+        <v>10.89</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B25">
-        <v>593</v>
-      </c>
-      <c r="C25">
-        <v>2.16</v>
-      </c>
-      <c r="D25">
-        <v>4.1</v>
-      </c>
-      <c r="E25">
-        <v>0.5</v>
-      </c>
-      <c r="F25">
-        <v>34.6</v>
-      </c>
-      <c r="G25">
+      <c r="B32">
+        <v>2310</v>
+      </c>
+      <c r="C32">
+        <v>8.41</v>
+      </c>
+      <c r="D32">
+        <v>13.51</v>
+      </c>
+      <c r="E32">
+        <v>0.5</v>
+      </c>
+      <c r="F32">
+        <v>91.31</v>
+      </c>
+      <c r="G32">
         <v>183</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>818</v>
+      </c>
+      <c r="C33">
+        <v>2.65</v>
+      </c>
+      <c r="D33">
+        <v>9.75</v>
+      </c>
+      <c r="E33">
+        <v>0.5</v>
+      </c>
+      <c r="F33">
+        <v>96.68000000000001</v>
+      </c>
+      <c r="G33">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Surgical Physician Assistant</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1618</v>
+      </c>
+      <c r="C34">
+        <v>7.19</v>
+      </c>
+      <c r="D34">
+        <v>12.19</v>
+      </c>
+      <c r="E34">
+        <v>0.5</v>
+      </c>
+      <c r="F34">
+        <v>84.94</v>
+      </c>
+      <c r="G34">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.92</v>
+      </c>
+      <c r="D35">
+        <v>2.49</v>
+      </c>
+      <c r="E35">
+        <v>0.5</v>
+      </c>
+      <c r="F35">
+        <v>10.74</v>
+      </c>
+      <c r="G35">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1048,19 +1293,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="D2">
-        <v>0.71</v>
+        <v>1.18</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1069,576 +1314,818 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Case Manager / Care Coordinator</t>
         </is>
       </c>
       <c r="B3">
-        <v>11862</v>
+        <v>487622</v>
       </c>
       <c r="C3">
-        <v>2.28</v>
+        <v>30.3</v>
       </c>
       <c r="D3">
-        <v>4.29</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>59.63</v>
+        <v>1027.27</v>
       </c>
       <c r="G3">
-        <v>3427</v>
+        <v>11466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B4">
-        <v>42901</v>
+        <v>50618</v>
       </c>
       <c r="C4">
-        <v>2.94</v>
+        <v>9.75</v>
       </c>
       <c r="D4">
-        <v>5.5</v>
+        <v>18.62</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>186.45</v>
+        <v>247.52</v>
       </c>
       <c r="G4">
-        <v>9405</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B5">
-        <v>22347</v>
+        <v>212202</v>
       </c>
       <c r="C5">
-        <v>5.27</v>
+        <v>14.56</v>
       </c>
       <c r="D5">
-        <v>9.630000000000001</v>
+        <v>25.92</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>77.48</v>
+        <v>557.4400000000001</v>
       </c>
       <c r="G5">
-        <v>2879</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>118532</v>
       </c>
       <c r="C6">
-        <v>2.22</v>
+        <v>27.97</v>
       </c>
       <c r="D6">
-        <v>3.9</v>
+        <v>69.36</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>14.05</v>
+        <v>1891.94</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B7">
-        <v>325922</v>
+        <v>383</v>
       </c>
       <c r="C7">
-        <v>11.23</v>
+        <v>9.43</v>
       </c>
       <c r="D7">
-        <v>12.66</v>
+        <v>16.39</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>166.11</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="G7">
-        <v>21658</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B8">
-        <v>51</v>
+        <v>909484</v>
       </c>
       <c r="C8">
-        <v>3.38</v>
+        <v>31.32</v>
       </c>
       <c r="D8">
-        <v>5.11</v>
+        <v>40.3</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>19.48</v>
+        <v>704.14</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>Health Information Technician</t>
         </is>
       </c>
       <c r="B9">
-        <v>36677</v>
+        <v>75271</v>
       </c>
       <c r="C9">
-        <v>5.05</v>
+        <v>22.06</v>
       </c>
       <c r="D9">
-        <v>9.73</v>
+        <v>37.62</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>112.76</v>
+        <v>319.59</v>
       </c>
       <c r="G9">
-        <v>4954</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>8.74</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>13.13</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>48.7</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B11">
-        <v>31006</v>
+        <v>120759</v>
       </c>
       <c r="C11">
-        <v>2.62</v>
+        <v>16.63</v>
       </c>
       <c r="D11">
-        <v>5.07</v>
+        <v>34.91</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>71.27</v>
+        <v>476.31</v>
       </c>
       <c r="G11">
-        <v>7891</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>621</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B13">
-        <v>1916</v>
+        <v>87733</v>
       </c>
       <c r="C13">
-        <v>2.01</v>
+        <v>7.42</v>
       </c>
       <c r="D13">
-        <v>4.21</v>
+        <v>16.56</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>44.54</v>
+        <v>419.65</v>
       </c>
       <c r="G13">
-        <v>616</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B14">
-        <v>426</v>
+        <v>9972</v>
       </c>
       <c r="C14">
-        <v>1.49</v>
+        <v>10.47</v>
       </c>
       <c r="D14">
-        <v>2.95</v>
+        <v>20.18</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>22.14</v>
+        <v>186.51</v>
       </c>
       <c r="G14">
-        <v>220</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Other Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>6094</v>
+        <v>831207</v>
       </c>
       <c r="C15">
-        <v>3.58</v>
+        <v>42.9</v>
       </c>
       <c r="D15">
-        <v>6.95</v>
+        <v>93.41</v>
       </c>
       <c r="E15">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F15">
-        <v>80.65000000000001</v>
+        <v>2557.75</v>
       </c>
       <c r="G15">
-        <v>1125</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B16">
-        <v>468</v>
+        <v>2150</v>
       </c>
       <c r="C16">
-        <v>1.73</v>
+        <v>7.5</v>
       </c>
       <c r="D16">
-        <v>2.8</v>
+        <v>18.93</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>23.95</v>
+        <v>114.79</v>
       </c>
       <c r="G16">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="B17">
-        <v>28368</v>
+        <v>14131</v>
       </c>
       <c r="C17">
-        <v>2.43</v>
+        <v>4.06</v>
       </c>
       <c r="D17">
-        <v>4.05</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>79.40000000000001</v>
+        <v>121.75</v>
       </c>
       <c r="G17">
-        <v>7644</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B18">
-        <v>112</v>
+        <v>19394</v>
       </c>
       <c r="C18">
-        <v>1.08</v>
+        <v>11.4</v>
       </c>
       <c r="D18">
-        <v>1.16</v>
+        <v>23.57</v>
       </c>
       <c r="E18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>5.5</v>
+        <v>267.26</v>
       </c>
       <c r="G18">
-        <v>61</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Phlebotomist</t>
         </is>
       </c>
       <c r="B19">
-        <v>141</v>
+        <v>17886</v>
       </c>
       <c r="C19">
-        <v>2.9</v>
+        <v>6.11</v>
       </c>
       <c r="D19">
-        <v>3.19</v>
+        <v>12.76</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>15.01</v>
+        <v>178.28</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B20">
-        <v>15197</v>
+        <v>1083</v>
       </c>
       <c r="C20">
-        <v>2.67</v>
+        <v>3.99</v>
       </c>
       <c r="D20">
-        <v>5.96</v>
+        <v>7.15</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>162.05</v>
+        <v>52.18</v>
       </c>
       <c r="G20">
-        <v>3731</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B21">
-        <v>75</v>
+        <v>356370</v>
       </c>
       <c r="C21">
-        <v>0.9</v>
+        <v>30.5</v>
       </c>
       <c r="D21">
-        <v>1.51</v>
+        <v>55.1</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F21">
-        <v>8.82</v>
+        <v>741.66</v>
       </c>
       <c r="G21">
-        <v>51</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Physician Office Based Coding Specialist</t>
         </is>
       </c>
       <c r="B22">
-        <v>3848</v>
+        <v>11740</v>
       </c>
       <c r="C22">
-        <v>2.2</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D22">
-        <v>5.01</v>
+        <v>21.27</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>77.04000000000001</v>
+        <v>213.38</v>
       </c>
       <c r="G22">
-        <v>1110</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B23">
-        <v>9644</v>
+        <v>807</v>
       </c>
       <c r="C23">
-        <v>2.48</v>
+        <v>7.81</v>
       </c>
       <c r="D23">
-        <v>5.83</v>
+        <v>7.41</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>146.1</v>
+        <v>42.69</v>
       </c>
       <c r="G23">
-        <v>2502</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>359</v>
       </c>
       <c r="C24">
-        <v>3.53</v>
+        <v>7.37</v>
       </c>
       <c r="D24">
-        <v>1.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E24">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="F24">
-        <v>4.36</v>
+        <v>46.03</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Radiography Technologist</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>52</v>
+      </c>
+      <c r="C25">
+        <v>4.21</v>
+      </c>
+      <c r="D25">
+        <v>2.33</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>6.95</v>
+      </c>
+      <c r="G25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Registered Community Health Nurse</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>72305</v>
+      </c>
+      <c r="C26">
+        <v>12.72</v>
+      </c>
+      <c r="D26">
+        <v>31.22</v>
+      </c>
+      <c r="E26">
+        <v>0.5</v>
+      </c>
+      <c r="F26">
+        <v>741.91</v>
+      </c>
+      <c r="G26">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Registered Dietitian</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>364</v>
+      </c>
+      <c r="C27">
+        <v>4.38</v>
+      </c>
+      <c r="D27">
+        <v>17.64</v>
+      </c>
+      <c r="E27">
+        <v>0.5</v>
+      </c>
+      <c r="F27">
+        <v>125.28</v>
+      </c>
+      <c r="G27">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Registered General Practice Nurse</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>37632</v>
+      </c>
+      <c r="C28">
+        <v>21.52</v>
+      </c>
+      <c r="D28">
+        <v>46.64</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>644.89</v>
+      </c>
+      <c r="G28">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Registered Nurse</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>48308</v>
+      </c>
+      <c r="C29">
+        <v>12.42</v>
+      </c>
+      <c r="D29">
+        <v>22.25</v>
+      </c>
+      <c r="E29">
+        <v>0.5</v>
+      </c>
+      <c r="F29">
+        <v>332.78</v>
+      </c>
+      <c r="G29">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Registered Record Administrator</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>325580</v>
+      </c>
+      <c r="C30">
+        <v>16.69</v>
+      </c>
+      <c r="D30">
+        <v>35.01</v>
+      </c>
+      <c r="E30">
+        <v>0.5</v>
+      </c>
+      <c r="F30">
+        <v>519.47</v>
+      </c>
+      <c r="G30">
+        <v>14045</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <v>8.06</v>
+      </c>
+      <c r="D31">
+        <v>6.54</v>
+      </c>
+      <c r="E31">
+        <v>1.65</v>
+      </c>
+      <c r="F31">
+        <v>10.89</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B25">
-        <v>593</v>
-      </c>
-      <c r="C25">
-        <v>2.16</v>
-      </c>
-      <c r="D25">
-        <v>4.1</v>
-      </c>
-      <c r="E25">
-        <v>0.5</v>
-      </c>
-      <c r="F25">
-        <v>34.6</v>
-      </c>
-      <c r="G25">
+      <c r="B32">
+        <v>2310</v>
+      </c>
+      <c r="C32">
+        <v>8.41</v>
+      </c>
+      <c r="D32">
+        <v>13.51</v>
+      </c>
+      <c r="E32">
+        <v>0.5</v>
+      </c>
+      <c r="F32">
+        <v>91.31</v>
+      </c>
+      <c r="G32">
         <v>183</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>818</v>
+      </c>
+      <c r="C33">
+        <v>2.65</v>
+      </c>
+      <c r="D33">
+        <v>9.75</v>
+      </c>
+      <c r="E33">
+        <v>0.5</v>
+      </c>
+      <c r="F33">
+        <v>96.68000000000001</v>
+      </c>
+      <c r="G33">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Surgical Physician Assistant</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1618</v>
+      </c>
+      <c r="C34">
+        <v>7.19</v>
+      </c>
+      <c r="D34">
+        <v>12.19</v>
+      </c>
+      <c r="E34">
+        <v>0.5</v>
+      </c>
+      <c r="F34">
+        <v>84.94</v>
+      </c>
+      <c r="G34">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.92</v>
+      </c>
+      <c r="D35">
+        <v>2.49</v>
+      </c>
+      <c r="E35">
+        <v>0.5</v>
+      </c>
+      <c r="F35">
+        <v>10.74</v>
       </c>
     </row>
   </sheetData>
@@ -1648,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1691,100 +2178,125 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Administrative Non-clinical</t>
         </is>
       </c>
       <c r="B2">
-        <v>397191</v>
+        <v>1720623</v>
       </c>
       <c r="C2">
-        <v>13.57</v>
+        <v>59.95</v>
       </c>
       <c r="D2">
-        <v>14.66</v>
+        <v>101.43</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>227.56</v>
+        <v>2834.94</v>
       </c>
       <c r="G2">
-        <v>21900</v>
+        <v>21325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>42557</v>
+        <v>1028274</v>
       </c>
       <c r="C3">
-        <v>3.02</v>
+        <v>35.28</v>
       </c>
       <c r="D3">
-        <v>6.14</v>
+        <v>43.42</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>162.05</v>
+        <v>778.5599999999999</v>
       </c>
       <c r="G3">
-        <v>9362</v>
+        <v>21774</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B4">
-        <v>67002</v>
+        <v>431420</v>
       </c>
       <c r="C4">
-        <v>5.37</v>
+        <v>18.36</v>
       </c>
       <c r="D4">
-        <v>9.93</v>
+        <v>32.96</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>112.76</v>
+        <v>741.91</v>
       </c>
       <c r="G4">
-        <v>8547</v>
+        <v>15613</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>537188</v>
+      </c>
+      <c r="C5">
+        <v>24.9</v>
+      </c>
+      <c r="D5">
+        <v>48.8</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>1928.73</v>
+      </c>
+      <c r="G5">
+        <v>14899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="B5">
-        <v>31006</v>
-      </c>
-      <c r="C5">
-        <v>2.62</v>
-      </c>
-      <c r="D5">
-        <v>5.07</v>
-      </c>
-      <c r="E5">
-        <v>0.5</v>
-      </c>
-      <c r="F5">
-        <v>71.27</v>
-      </c>
-      <c r="G5">
+      <c r="B6">
+        <v>87733</v>
+      </c>
+      <c r="C6">
+        <v>7.42</v>
+      </c>
+      <c r="D6">
+        <v>16.56</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>419.65</v>
+      </c>
+      <c r="G6">
         <v>7891</v>
       </c>
     </row>
@@ -1795,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1838,51 +2350,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Administrative Non-clinical</t>
         </is>
       </c>
       <c r="B2">
-        <v>397191</v>
+        <v>1732238</v>
       </c>
       <c r="C2">
-        <v>13.57</v>
+        <v>59.88</v>
       </c>
       <c r="D2">
-        <v>14.66</v>
+        <v>101.55</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>227.56</v>
+        <v>2834.94</v>
       </c>
       <c r="G2">
-        <v>21900</v>
+        <v>21822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1028274</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>35.28</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>43.42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>778.5599999999999</v>
       </c>
       <c r="G3">
-        <v>621</v>
+        <v>21774</v>
       </c>
     </row>
     <row r="4">
@@ -1892,22 +2404,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>42557</v>
+        <v>431420</v>
       </c>
       <c r="C4">
-        <v>3.02</v>
+        <v>18.36</v>
       </c>
       <c r="D4">
-        <v>6.14</v>
+        <v>32.96</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>162.05</v>
+        <v>741.91</v>
       </c>
       <c r="G4">
-        <v>9362</v>
+        <v>15613</v>
       </c>
     </row>
     <row r="5">
@@ -1917,22 +2429,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>67002</v>
+        <v>537188</v>
       </c>
       <c r="C5">
-        <v>5.37</v>
+        <v>24.9</v>
       </c>
       <c r="D5">
-        <v>9.93</v>
+        <v>48.8</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>112.76</v>
+        <v>1928.73</v>
       </c>
       <c r="G5">
-        <v>8547</v>
+        <v>14899</v>
       </c>
     </row>
     <row r="6">
@@ -1942,22 +2454,39 @@
         </is>
       </c>
       <c r="B6">
-        <v>31006</v>
+        <v>87733</v>
       </c>
       <c r="C6">
-        <v>2.62</v>
+        <v>7.42</v>
       </c>
       <c r="D6">
-        <v>5.07</v>
+        <v>16.56</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>71.27</v>
+        <v>419.65</v>
       </c>
       <c r="G6">
         <v>7891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7">
+        <v>102</v>
+      </c>
+      <c r="C7">
+        <v>0.92</v>
+      </c>
+      <c r="D7">
+        <v>2.49</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
+        <v>10.74</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,19 +401,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1.18</v>
+        <v>0.71</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -422,821 +422,576 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Case Manager / Care Coordinator</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B3">
-        <v>487622</v>
+        <v>11862</v>
       </c>
       <c r="C3">
-        <v>30.3</v>
+        <v>2.28</v>
       </c>
       <c r="D3">
-        <v>68.65000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
-        <v>1027.27</v>
+        <v>59.63</v>
       </c>
       <c r="G3">
-        <v>11466</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B4">
-        <v>50618</v>
+        <v>42901</v>
       </c>
       <c r="C4">
-        <v>9.75</v>
+        <v>2.94</v>
       </c>
       <c r="D4">
-        <v>18.62</v>
+        <v>5.5</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>247.52</v>
+        <v>186.45</v>
       </c>
       <c r="G4">
-        <v>3427</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B5">
-        <v>212202</v>
+        <v>22347</v>
       </c>
       <c r="C5">
-        <v>14.56</v>
+        <v>5.27</v>
       </c>
       <c r="D5">
-        <v>25.92</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>557.4400000000001</v>
+        <v>77.48</v>
       </c>
       <c r="G5">
-        <v>9405</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B6">
-        <v>118532</v>
+        <v>90</v>
       </c>
       <c r="C6">
-        <v>27.97</v>
+        <v>2.22</v>
       </c>
       <c r="D6">
-        <v>69.36</v>
+        <v>3.9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
-        <v>1891.94</v>
+        <v>14.05</v>
       </c>
       <c r="G6">
-        <v>2879</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B7">
-        <v>383</v>
+        <v>325922</v>
       </c>
       <c r="C7">
-        <v>9.43</v>
+        <v>11.23</v>
       </c>
       <c r="D7">
-        <v>16.39</v>
+        <v>12.66</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>84.29000000000001</v>
+        <v>166.11</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B8">
-        <v>909484</v>
+        <v>51</v>
       </c>
       <c r="C8">
-        <v>31.32</v>
+        <v>3.38</v>
       </c>
       <c r="D8">
-        <v>40.3</v>
+        <v>5.11</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>704.14</v>
+        <v>19.48</v>
       </c>
       <c r="G8">
-        <v>21658</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Health Information Technician</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B9">
-        <v>75271</v>
+        <v>36677</v>
       </c>
       <c r="C9">
-        <v>22.06</v>
+        <v>5.05</v>
       </c>
       <c r="D9">
-        <v>37.62</v>
+        <v>9.73</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>319.59</v>
+        <v>112.76</v>
       </c>
       <c r="G9">
-        <v>2483</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B10">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>8.74</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>13.13</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>48.7</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>120759</v>
+        <v>31006</v>
       </c>
       <c r="C11">
-        <v>16.63</v>
+        <v>2.62</v>
       </c>
       <c r="D11">
-        <v>34.91</v>
+        <v>5.07</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>476.31</v>
+        <v>71.27</v>
       </c>
       <c r="G11">
-        <v>4954</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>22119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B13">
-        <v>87733</v>
+        <v>1916</v>
       </c>
       <c r="C13">
-        <v>7.42</v>
+        <v>2.01</v>
       </c>
       <c r="D13">
-        <v>16.56</v>
+        <v>4.21</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>419.65</v>
+        <v>44.54</v>
       </c>
       <c r="G13">
-        <v>7891</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B14">
-        <v>9972</v>
+        <v>426</v>
       </c>
       <c r="C14">
-        <v>10.47</v>
+        <v>1.49</v>
       </c>
       <c r="D14">
-        <v>20.18</v>
+        <v>2.95</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>186.51</v>
+        <v>22.14</v>
       </c>
       <c r="G14">
-        <v>616</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Other Technician</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>831207</v>
+        <v>6094</v>
       </c>
       <c r="C15">
-        <v>42.9</v>
+        <v>3.58</v>
       </c>
       <c r="D15">
-        <v>93.41</v>
+        <v>6.95</v>
       </c>
       <c r="E15">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>2557.75</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G15">
-        <v>13746</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B16">
-        <v>2150</v>
+        <v>468</v>
       </c>
       <c r="C16">
-        <v>7.5</v>
+        <v>1.73</v>
       </c>
       <c r="D16">
-        <v>18.93</v>
+        <v>2.8</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>114.79</v>
+        <v>23.95</v>
       </c>
       <c r="G16">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B17">
-        <v>14131</v>
+        <v>28368</v>
       </c>
       <c r="C17">
-        <v>4.06</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>8.369999999999999</v>
+        <v>4.05</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>121.75</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17">
-        <v>2410</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B18">
-        <v>19394</v>
+        <v>112</v>
       </c>
       <c r="C18">
-        <v>11.4</v>
+        <v>1.08</v>
       </c>
       <c r="D18">
-        <v>23.57</v>
+        <v>1.16</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
-        <v>267.26</v>
+        <v>5.5</v>
       </c>
       <c r="G18">
-        <v>1125</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B19">
-        <v>17886</v>
+        <v>141</v>
       </c>
       <c r="C19">
-        <v>6.11</v>
+        <v>2.9</v>
       </c>
       <c r="D19">
-        <v>12.76</v>
+        <v>3.19</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>178.28</v>
+        <v>15.01</v>
       </c>
       <c r="G19">
-        <v>1877</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B20">
-        <v>1083</v>
+        <v>15197</v>
       </c>
       <c r="C20">
-        <v>3.99</v>
+        <v>2.67</v>
       </c>
       <c r="D20">
-        <v>7.15</v>
+        <v>5.96</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>52.18</v>
+        <v>162.05</v>
       </c>
       <c r="G20">
-        <v>175</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B21">
-        <v>356370</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <v>30.5</v>
+        <v>0.9</v>
       </c>
       <c r="D21">
-        <v>55.1</v>
+        <v>1.51</v>
       </c>
       <c r="E21">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>741.66</v>
+        <v>8.82</v>
       </c>
       <c r="G21">
-        <v>7644</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Physician Office Based Coding Specialist</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>11740</v>
+        <v>3848</v>
       </c>
       <c r="C22">
-        <v>9.119999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="D22">
-        <v>21.27</v>
+        <v>5.01</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>213.38</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>916</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B23">
-        <v>807</v>
+        <v>9644</v>
       </c>
       <c r="C23">
-        <v>7.81</v>
+        <v>2.48</v>
       </c>
       <c r="D23">
-        <v>7.41</v>
+        <v>5.83</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>42.69</v>
+        <v>146.1</v>
       </c>
       <c r="G23">
-        <v>61</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B24">
-        <v>359</v>
+        <v>7</v>
       </c>
       <c r="C24">
-        <v>7.37</v>
+        <v>3.53</v>
       </c>
       <c r="D24">
-        <v>9.890000000000001</v>
+        <v>1.92</v>
       </c>
       <c r="E24">
-        <v>0.5</v>
+        <v>1.65</v>
       </c>
       <c r="F24">
-        <v>46.03</v>
+        <v>4.36</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Radiography Technologist</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="B25">
-        <v>52</v>
+        <v>593</v>
       </c>
       <c r="C25">
-        <v>4.21</v>
+        <v>2.16</v>
       </c>
       <c r="D25">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>6.95</v>
+        <v>34.6</v>
       </c>
       <c r="G25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Registered Community Health Nurse</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>72305</v>
-      </c>
-      <c r="C26">
-        <v>12.72</v>
-      </c>
-      <c r="D26">
-        <v>31.22</v>
-      </c>
-      <c r="E26">
-        <v>0.5</v>
-      </c>
-      <c r="F26">
-        <v>741.91</v>
-      </c>
-      <c r="G26">
-        <v>3731</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Registered Dietitian</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>364</v>
-      </c>
-      <c r="C27">
-        <v>4.38</v>
-      </c>
-      <c r="D27">
-        <v>17.64</v>
-      </c>
-      <c r="E27">
-        <v>0.5</v>
-      </c>
-      <c r="F27">
-        <v>125.28</v>
-      </c>
-      <c r="G27">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Registered General Practice Nurse</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>37632</v>
-      </c>
-      <c r="C28">
-        <v>21.52</v>
-      </c>
-      <c r="D28">
-        <v>46.64</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>644.89</v>
-      </c>
-      <c r="G28">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Registered Nurse</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>48308</v>
-      </c>
-      <c r="C29">
-        <v>12.42</v>
-      </c>
-      <c r="D29">
-        <v>22.25</v>
-      </c>
-      <c r="E29">
-        <v>0.5</v>
-      </c>
-      <c r="F29">
-        <v>332.78</v>
-      </c>
-      <c r="G29">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Registered Record Administrator</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>325580</v>
-      </c>
-      <c r="C30">
-        <v>16.69</v>
-      </c>
-      <c r="D30">
-        <v>35.01</v>
-      </c>
-      <c r="E30">
-        <v>0.5</v>
-      </c>
-      <c r="F30">
-        <v>519.47</v>
-      </c>
-      <c r="G30">
-        <v>14045</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>16</v>
-      </c>
-      <c r="C31">
-        <v>8.06</v>
-      </c>
-      <c r="D31">
-        <v>6.54</v>
-      </c>
-      <c r="E31">
-        <v>1.65</v>
-      </c>
-      <c r="F31">
-        <v>10.89</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>2310</v>
-      </c>
-      <c r="C32">
-        <v>8.41</v>
-      </c>
-      <c r="D32">
-        <v>13.51</v>
-      </c>
-      <c r="E32">
-        <v>0.5</v>
-      </c>
-      <c r="F32">
-        <v>91.31</v>
-      </c>
-      <c r="G32">
         <v>183</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>818</v>
-      </c>
-      <c r="C33">
-        <v>2.65</v>
-      </c>
-      <c r="D33">
-        <v>9.75</v>
-      </c>
-      <c r="E33">
-        <v>0.5</v>
-      </c>
-      <c r="F33">
-        <v>96.68000000000001</v>
-      </c>
-      <c r="G33">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Surgical Physician Assistant</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>1618</v>
-      </c>
-      <c r="C34">
-        <v>7.19</v>
-      </c>
-      <c r="D34">
-        <v>12.19</v>
-      </c>
-      <c r="E34">
-        <v>0.5</v>
-      </c>
-      <c r="F34">
-        <v>84.94</v>
-      </c>
-      <c r="G34">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35">
-        <v>102</v>
-      </c>
-      <c r="C35">
-        <v>0.92</v>
-      </c>
-      <c r="D35">
-        <v>2.49</v>
-      </c>
-      <c r="E35">
-        <v>0.5</v>
-      </c>
-      <c r="F35">
-        <v>10.74</v>
-      </c>
-      <c r="G35">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1293,19 +1048,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1.18</v>
+        <v>0.71</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1314,818 +1069,576 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Case Manager / Care Coordinator</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B3">
-        <v>487622</v>
+        <v>11862</v>
       </c>
       <c r="C3">
-        <v>30.3</v>
+        <v>2.28</v>
       </c>
       <c r="D3">
-        <v>68.65000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
-        <v>1027.27</v>
+        <v>59.63</v>
       </c>
       <c r="G3">
-        <v>11466</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B4">
-        <v>50618</v>
+        <v>42901</v>
       </c>
       <c r="C4">
-        <v>9.75</v>
+        <v>2.94</v>
       </c>
       <c r="D4">
-        <v>18.62</v>
+        <v>5.5</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>247.52</v>
+        <v>186.45</v>
       </c>
       <c r="G4">
-        <v>3427</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B5">
-        <v>212202</v>
+        <v>22347</v>
       </c>
       <c r="C5">
-        <v>14.56</v>
+        <v>5.27</v>
       </c>
       <c r="D5">
-        <v>25.92</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>557.4400000000001</v>
+        <v>77.48</v>
       </c>
       <c r="G5">
-        <v>9405</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B6">
-        <v>118532</v>
+        <v>90</v>
       </c>
       <c r="C6">
-        <v>27.97</v>
+        <v>2.22</v>
       </c>
       <c r="D6">
-        <v>69.36</v>
+        <v>3.9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
-        <v>1891.94</v>
+        <v>14.05</v>
       </c>
       <c r="G6">
-        <v>2879</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B7">
-        <v>383</v>
+        <v>325922</v>
       </c>
       <c r="C7">
-        <v>9.43</v>
+        <v>11.23</v>
       </c>
       <c r="D7">
-        <v>16.39</v>
+        <v>12.66</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>84.29000000000001</v>
+        <v>166.11</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B8">
-        <v>909484</v>
+        <v>51</v>
       </c>
       <c r="C8">
-        <v>31.32</v>
+        <v>3.38</v>
       </c>
       <c r="D8">
-        <v>40.3</v>
+        <v>5.11</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>704.14</v>
+        <v>19.48</v>
       </c>
       <c r="G8">
-        <v>21658</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Health Information Technician</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B9">
-        <v>75271</v>
+        <v>36677</v>
       </c>
       <c r="C9">
-        <v>22.06</v>
+        <v>5.05</v>
       </c>
       <c r="D9">
-        <v>37.62</v>
+        <v>9.73</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>319.59</v>
+        <v>112.76</v>
       </c>
       <c r="G9">
-        <v>2483</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B10">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>8.74</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>13.13</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>48.7</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>120759</v>
+        <v>31006</v>
       </c>
       <c r="C11">
-        <v>16.63</v>
+        <v>2.62</v>
       </c>
       <c r="D11">
-        <v>34.91</v>
+        <v>5.07</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>476.31</v>
+        <v>71.27</v>
       </c>
       <c r="G11">
-        <v>4954</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>621</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B13">
-        <v>87733</v>
+        <v>1916</v>
       </c>
       <c r="C13">
-        <v>7.42</v>
+        <v>2.01</v>
       </c>
       <c r="D13">
-        <v>16.56</v>
+        <v>4.21</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>419.65</v>
+        <v>44.54</v>
       </c>
       <c r="G13">
-        <v>7891</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B14">
-        <v>9972</v>
+        <v>426</v>
       </c>
       <c r="C14">
-        <v>10.47</v>
+        <v>1.49</v>
       </c>
       <c r="D14">
-        <v>20.18</v>
+        <v>2.95</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>186.51</v>
+        <v>22.14</v>
       </c>
       <c r="G14">
-        <v>616</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Other Technician</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>831207</v>
+        <v>6094</v>
       </c>
       <c r="C15">
-        <v>42.9</v>
+        <v>3.58</v>
       </c>
       <c r="D15">
-        <v>93.41</v>
+        <v>6.95</v>
       </c>
       <c r="E15">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>2557.75</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G15">
-        <v>13746</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B16">
-        <v>2150</v>
+        <v>468</v>
       </c>
       <c r="C16">
-        <v>7.5</v>
+        <v>1.73</v>
       </c>
       <c r="D16">
-        <v>18.93</v>
+        <v>2.8</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>114.79</v>
+        <v>23.95</v>
       </c>
       <c r="G16">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B17">
-        <v>14131</v>
+        <v>28368</v>
       </c>
       <c r="C17">
-        <v>4.06</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>8.369999999999999</v>
+        <v>4.05</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>121.75</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17">
-        <v>2410</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B18">
-        <v>19394</v>
+        <v>112</v>
       </c>
       <c r="C18">
-        <v>11.4</v>
+        <v>1.08</v>
       </c>
       <c r="D18">
-        <v>23.57</v>
+        <v>1.16</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
-        <v>267.26</v>
+        <v>5.5</v>
       </c>
       <c r="G18">
-        <v>1125</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B19">
-        <v>17886</v>
+        <v>141</v>
       </c>
       <c r="C19">
-        <v>6.11</v>
+        <v>2.9</v>
       </c>
       <c r="D19">
-        <v>12.76</v>
+        <v>3.19</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>178.28</v>
+        <v>15.01</v>
       </c>
       <c r="G19">
-        <v>1877</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B20">
-        <v>1083</v>
+        <v>15197</v>
       </c>
       <c r="C20">
-        <v>3.99</v>
+        <v>2.67</v>
       </c>
       <c r="D20">
-        <v>7.15</v>
+        <v>5.96</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>52.18</v>
+        <v>162.05</v>
       </c>
       <c r="G20">
-        <v>175</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B21">
-        <v>356370</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <v>30.5</v>
+        <v>0.9</v>
       </c>
       <c r="D21">
-        <v>55.1</v>
+        <v>1.51</v>
       </c>
       <c r="E21">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>741.66</v>
+        <v>8.82</v>
       </c>
       <c r="G21">
-        <v>7644</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Physician Office Based Coding Specialist</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>11740</v>
+        <v>3848</v>
       </c>
       <c r="C22">
-        <v>9.119999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="D22">
-        <v>21.27</v>
+        <v>5.01</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>213.38</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>916</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B23">
-        <v>807</v>
+        <v>9644</v>
       </c>
       <c r="C23">
-        <v>7.81</v>
+        <v>2.48</v>
       </c>
       <c r="D23">
-        <v>7.41</v>
+        <v>5.83</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>42.69</v>
+        <v>146.1</v>
       </c>
       <c r="G23">
-        <v>61</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B24">
-        <v>359</v>
+        <v>7</v>
       </c>
       <c r="C24">
-        <v>7.37</v>
+        <v>3.53</v>
       </c>
       <c r="D24">
-        <v>9.890000000000001</v>
+        <v>1.92</v>
       </c>
       <c r="E24">
-        <v>0.5</v>
+        <v>1.65</v>
       </c>
       <c r="F24">
-        <v>46.03</v>
+        <v>4.36</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Radiography Technologist</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="B25">
-        <v>52</v>
+        <v>593</v>
       </c>
       <c r="C25">
-        <v>4.21</v>
+        <v>2.16</v>
       </c>
       <c r="D25">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>6.95</v>
+        <v>34.6</v>
       </c>
       <c r="G25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Registered Community Health Nurse</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>72305</v>
-      </c>
-      <c r="C26">
-        <v>12.72</v>
-      </c>
-      <c r="D26">
-        <v>31.22</v>
-      </c>
-      <c r="E26">
-        <v>0.5</v>
-      </c>
-      <c r="F26">
-        <v>741.91</v>
-      </c>
-      <c r="G26">
-        <v>3731</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Registered Dietitian</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>364</v>
-      </c>
-      <c r="C27">
-        <v>4.38</v>
-      </c>
-      <c r="D27">
-        <v>17.64</v>
-      </c>
-      <c r="E27">
-        <v>0.5</v>
-      </c>
-      <c r="F27">
-        <v>125.28</v>
-      </c>
-      <c r="G27">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Registered General Practice Nurse</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>37632</v>
-      </c>
-      <c r="C28">
-        <v>21.52</v>
-      </c>
-      <c r="D28">
-        <v>46.64</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>644.89</v>
-      </c>
-      <c r="G28">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Registered Nurse</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>48308</v>
-      </c>
-      <c r="C29">
-        <v>12.42</v>
-      </c>
-      <c r="D29">
-        <v>22.25</v>
-      </c>
-      <c r="E29">
-        <v>0.5</v>
-      </c>
-      <c r="F29">
-        <v>332.78</v>
-      </c>
-      <c r="G29">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Registered Record Administrator</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>325580</v>
-      </c>
-      <c r="C30">
-        <v>16.69</v>
-      </c>
-      <c r="D30">
-        <v>35.01</v>
-      </c>
-      <c r="E30">
-        <v>0.5</v>
-      </c>
-      <c r="F30">
-        <v>519.47</v>
-      </c>
-      <c r="G30">
-        <v>14045</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>16</v>
-      </c>
-      <c r="C31">
-        <v>8.06</v>
-      </c>
-      <c r="D31">
-        <v>6.54</v>
-      </c>
-      <c r="E31">
-        <v>1.65</v>
-      </c>
-      <c r="F31">
-        <v>10.89</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>2310</v>
-      </c>
-      <c r="C32">
-        <v>8.41</v>
-      </c>
-      <c r="D32">
-        <v>13.51</v>
-      </c>
-      <c r="E32">
-        <v>0.5</v>
-      </c>
-      <c r="F32">
-        <v>91.31</v>
-      </c>
-      <c r="G32">
         <v>183</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>818</v>
-      </c>
-      <c r="C33">
-        <v>2.65</v>
-      </c>
-      <c r="D33">
-        <v>9.75</v>
-      </c>
-      <c r="E33">
-        <v>0.5</v>
-      </c>
-      <c r="F33">
-        <v>96.68000000000001</v>
-      </c>
-      <c r="G33">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Surgical Physician Assistant</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>1618</v>
-      </c>
-      <c r="C34">
-        <v>7.19</v>
-      </c>
-      <c r="D34">
-        <v>12.19</v>
-      </c>
-      <c r="E34">
-        <v>0.5</v>
-      </c>
-      <c r="F34">
-        <v>84.94</v>
-      </c>
-      <c r="G34">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35">
-        <v>102</v>
-      </c>
-      <c r="C35">
-        <v>0.92</v>
-      </c>
-      <c r="D35">
-        <v>2.49</v>
-      </c>
-      <c r="E35">
-        <v>0.5</v>
-      </c>
-      <c r="F35">
-        <v>10.74</v>
       </c>
     </row>
   </sheetData>
@@ -2135,7 +1648,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2178,125 +1691,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>1720623</v>
+        <v>397191</v>
       </c>
       <c r="C2">
-        <v>59.95</v>
+        <v>13.57</v>
       </c>
       <c r="D2">
-        <v>101.43</v>
+        <v>14.66</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>2834.94</v>
+        <v>227.56</v>
       </c>
       <c r="G2">
-        <v>21325</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B3">
-        <v>1028274</v>
+        <v>42557</v>
       </c>
       <c r="C3">
-        <v>35.28</v>
+        <v>3.02</v>
       </c>
       <c r="D3">
-        <v>43.42</v>
+        <v>6.14</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>778.5599999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G3">
-        <v>21774</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B4">
-        <v>431420</v>
+        <v>67002</v>
       </c>
       <c r="C4">
-        <v>18.36</v>
+        <v>5.37</v>
       </c>
       <c r="D4">
-        <v>32.96</v>
+        <v>9.93</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>741.91</v>
+        <v>112.76</v>
       </c>
       <c r="G4">
-        <v>15613</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="B5">
-        <v>537188</v>
+        <v>31006</v>
       </c>
       <c r="C5">
-        <v>24.9</v>
+        <v>2.62</v>
       </c>
       <c r="D5">
-        <v>48.8</v>
+        <v>5.07</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>1928.73</v>
+        <v>71.27</v>
       </c>
       <c r="G5">
-        <v>14899</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Uncategorised</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>87733</v>
-      </c>
-      <c r="C6">
-        <v>7.42</v>
-      </c>
-      <c r="D6">
-        <v>16.56</v>
-      </c>
-      <c r="E6">
-        <v>0.5</v>
-      </c>
-      <c r="F6">
-        <v>419.65</v>
-      </c>
-      <c r="G6">
         <v>7891</v>
       </c>
     </row>
@@ -2307,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2350,51 +1838,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>1732238</v>
+        <v>397191</v>
       </c>
       <c r="C2">
-        <v>59.88</v>
+        <v>13.57</v>
       </c>
       <c r="D2">
-        <v>101.55</v>
+        <v>14.66</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>2834.94</v>
+        <v>227.56</v>
       </c>
       <c r="G2">
-        <v>21822</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B3">
-        <v>1028274</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>35.28</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>43.42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>778.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>21774</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4">
@@ -2404,22 +1892,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>431420</v>
+        <v>42557</v>
       </c>
       <c r="C4">
-        <v>18.36</v>
+        <v>3.02</v>
       </c>
       <c r="D4">
-        <v>32.96</v>
+        <v>6.14</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>741.91</v>
+        <v>162.05</v>
       </c>
       <c r="G4">
-        <v>15613</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="5">
@@ -2429,22 +1917,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>537188</v>
+        <v>67002</v>
       </c>
       <c r="C5">
-        <v>24.9</v>
+        <v>5.37</v>
       </c>
       <c r="D5">
-        <v>48.8</v>
+        <v>9.93</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>1928.73</v>
+        <v>112.76</v>
       </c>
       <c r="G5">
-        <v>14899</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="6">
@@ -2454,39 +1942,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>87733</v>
+        <v>31006</v>
       </c>
       <c r="C6">
-        <v>7.42</v>
+        <v>2.62</v>
       </c>
       <c r="D6">
-        <v>16.56</v>
+        <v>5.07</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>419.65</v>
+        <v>71.27</v>
       </c>
       <c r="G6">
         <v>7891</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7">
-        <v>102</v>
-      </c>
-      <c r="C7">
-        <v>0.92</v>
-      </c>
-      <c r="D7">
-        <v>2.49</v>
-      </c>
-      <c r="E7">
-        <v>0.5</v>
-      </c>
-      <c r="F7">
-        <v>10.74</v>
       </c>
     </row>
   </sheetData>
